--- a/manual_matches.xlsx
+++ b/manual_matches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtafoya\Projects\camd-eia-crosswalk-github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\capd_eia_crosswalk\users\zhangm\camd-eia-crosswalk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61992D5-9679-4AAE-BF9F-E7D6514B8087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC81CDD0-E737-4305-BC2D-C2CCC8F6CACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_manual_matches" sheetId="1" r:id="rId1"/>
@@ -42,15 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="416">
   <si>
-    <t>CAMD_PLANT_ID</t>
-  </si>
-  <si>
-    <t>CAMD_UNIT_ID</t>
-  </si>
-  <si>
-    <t>CAMD_GENERATOR_ID</t>
-  </si>
-  <si>
     <t>EIA_PLANT_ID</t>
   </si>
   <si>
@@ -1014,9 +1005,6 @@
     <t>P049</t>
   </si>
   <si>
-    <t>CAMD_PLANT_NAME</t>
-  </si>
-  <si>
     <t>EIA_PLANT_NAME</t>
   </si>
   <si>
@@ -1152,21 +1140,12 @@
     <t>unit_manual_matches</t>
   </si>
   <si>
-    <t xml:space="preserve">This sheet contains manual matches made between EIA/CAMD unit-generator identifiers and EIA boiler-generator identifiers. The EIA_BOILER_ID is optional, but the EIA_GENERATOR_ID is required for a match to occur. Any new entries should include notes justifying this match. Any user of this crosswalk can add to this manual match list. It is advised to run the crosswalk R script to check that the manual matches produce the intended results and then submit a pull request. </t>
-  </si>
-  <si>
     <t>unit_manual_excluded</t>
   </si>
   <si>
-    <t xml:space="preserve">This sheet contains unique CAMD plant-unit-generator identifiers that should be excluded from the automated matching process due to the production of mismatches or due to the generator not being grid connected, which would preclude the generator from appearing in the EIA data. Here only the CAMD identifiers are required. Any new entries should include notes justifying this match. Any user of this crosswalk can add to this manual match list. It is advised to run the crosswalk R script to check that the manual matches produce the intended results and then submit a pull request. </t>
-  </si>
-  <si>
     <t>plant_id_manual_matches</t>
   </si>
   <si>
-    <t>In rare instances, the ORIS/plant codes do not match in CAMD and EIA’s databases. These discrepancies were discovered through the production of eGRID (https://www.epa.gov/egrid) and are regularly tracked and updated with new eGRID releases. In the crosswalk code, these discrepancies are accounted for before any matching occurs. In the code, CAMD changes EIA’s plant code to match CAMD’s ORIS code and includes a field indicating that the plant code has been changed (“PLANT_ID_CHANGE_FLAG”). This sheet is updated with any changes to Table C-5 of Appendix C in the eGRID2018 TSD (https://www.epa.gov/egrid/egrid-technical-support-document). A direct download for this table in xlsx format can be found here: [epa-eia_plant_id_crosswalk.xlsx](https://www.epa.gov/sites/production/files/2020-09/epa-eia_plant_id_crosswalk.xlsx).</t>
-  </si>
-  <si>
     <t>Unit supplies electricity to Mexico exclusively, not in EIA-860 as of 2018. https://www.spglobal.com/marketintelligence/en/news-insights/trending/sbkd29axoy7kb_xbetu4dw2</t>
   </si>
   <si>
@@ -1287,7 +1266,28 @@
     <t>further_research</t>
   </si>
   <si>
-    <t>These units exist in CAMD without a generator ID. They are likely industrial units and not in the EIA database, but we welcome research or information on these units</t>
+    <t>EPA_PLANT_ID</t>
+  </si>
+  <si>
+    <t>EPA_UNIT_ID</t>
+  </si>
+  <si>
+    <t>EPA_GENERATOR_ID</t>
+  </si>
+  <si>
+    <t>EPA_PLANT_NAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This sheet contains manual matches made between EIA/EPA unit-generator identifiers and EIA boiler-generator identifiers. The EIA_BOILER_ID is optional, but the EIA_GENERATOR_ID is required for a match to occur. Any new entries should include notes justifying this match. Any user of this crosswalk can add to this manual match list. It is advised to run the crosswalk R script to check that the manual matches produce the intended results and then submit a pull request. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This sheet contains unique EPA plant-unit-generator identifiers that should be excluded from the automated matching process due to the production of mismatches or due to the generator not being grid connected, which would preclude the generator from appearing in the EIA data. Here only the EPA identifiers are required. Any new entries should include notes justifying this match. Any user of this crosswalk can add to this manual match list. It is advised to run the crosswalk R script to check that the manual matches produce the intended results and then submit a pull request. </t>
+  </si>
+  <si>
+    <t>In rare instances, the ORIS/plant codes do not match in EPA and EIA’s databases. These discrepancies were discovered through the production of eGRID (https://www.epa.gov/egrid) and are regularly tracked and updated with new eGRID releases. In the crosswalk code, these discrepancies are accounted for before any matching occurs. In the code, CAMD changes EIA’s plant code to match CAMD’s ORIS code and includes a field indicating that the plant code has been changed (“PLANT_ID_CHANGE_FLAG”). This sheet is updated with any changes to Table C-5 of Appendix C in the eGRID2018 TSD (https://www.epa.gov/egrid/egrid-technical-support-document). A direct download for this table in xlsx format can be found here: [epa-eia_plant_id_crosswalk.xlsx](https://www.epa.gov/sites/production/files/2020-09/epa-eia_plant_id_crosswalk.xlsx).</t>
+  </si>
+  <si>
+    <t>These units exist in EPA without a generator ID. They are likely industrial units and not in the EIA database, but we welcome research or information on these units</t>
   </si>
 </sst>
 </file>
@@ -1796,7 +1796,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1818,7 +1818,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1840,19 +1840,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1912,9 +1899,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1952,7 +1939,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2058,7 +2045,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2200,7 +2187,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2222,25 +2209,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="G1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -2263,7 +2250,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2286,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2294,22 +2281,22 @@
         <v>50030</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" s="6">
         <v>1393</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2317,22 +2304,22 @@
         <v>50030</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="6">
         <v>1393</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2343,111 +2330,111 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" s="6">
         <v>1403</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>1702</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1702</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>1702</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1702</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>1702</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1702</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+      <c r="G9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>1702</v>
       </c>
-      <c r="B7" s="21">
-        <v>1</v>
-      </c>
-      <c r="C7" s="21">
-        <v>1</v>
-      </c>
-      <c r="D7" s="20">
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6">
         <v>1702</v>
       </c>
-      <c r="E7" s="21">
-        <v>1</v>
-      </c>
-      <c r="F7" s="22" t="s">
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="23" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
-        <v>1702</v>
-      </c>
-      <c r="B8" s="21">
-        <v>1</v>
-      </c>
-      <c r="C8" s="21">
-        <v>1</v>
-      </c>
-      <c r="D8" s="20">
-        <v>1702</v>
-      </c>
-      <c r="E8" s="21">
-        <v>1</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
-        <v>1702</v>
-      </c>
-      <c r="B9" s="21">
-        <v>2</v>
-      </c>
-      <c r="C9" s="21">
-        <v>2</v>
-      </c>
-      <c r="D9" s="20">
-        <v>1702</v>
-      </c>
-      <c r="E9" s="21">
-        <v>2</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
-        <v>1702</v>
-      </c>
-      <c r="B10" s="21">
-        <v>2</v>
-      </c>
-      <c r="C10" s="21">
-        <v>2</v>
-      </c>
-      <c r="D10" s="20">
-        <v>1702</v>
-      </c>
-      <c r="E10" s="21">
-        <v>2</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>403</v>
+      <c r="G10" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2455,10 +2442,10 @@
         <v>3612</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D11" s="7">
         <v>7512</v>
@@ -2467,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2475,22 +2462,22 @@
         <v>3612</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12" s="7">
         <v>7512</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F12" s="5">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2498,22 +2485,22 @@
         <v>3612</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D13" s="7">
         <v>7512</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F13" s="5">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2521,10 +2508,10 @@
         <v>3612</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D14" s="7">
         <v>7512</v>
@@ -2533,7 +2520,7 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2541,19 +2528,19 @@
         <v>2709</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D15" s="6">
         <v>7538</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2561,19 +2548,19 @@
         <v>2709</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D16" s="6">
         <v>7538</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
         <v>20</v>
-      </c>
-      <c r="G16" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2581,19 +2568,19 @@
         <v>2709</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6">
         <v>7538</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2601,19 +2588,19 @@
         <v>2709</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D18" s="6">
         <v>7538</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2621,61 +2608,59 @@
         <v>2709</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D19" s="6">
         <v>7538</v>
       </c>
       <c r="F19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>7903</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D20" s="6">
+        <v>7903</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>7903</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
+      <c r="C21" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D21" s="6">
         <v>7903</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="D20" s="20">
-        <v>7903</v>
-      </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
-        <v>7903</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="D21" s="20">
-        <v>7903</v>
-      </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>404</v>
+      <c r="F21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2683,10 +2668,10 @@
         <v>7350</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D22" s="6">
         <v>7931</v>
@@ -2695,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2703,22 +2688,22 @@
         <v>7350</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="D23" s="6">
         <v>7931</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F23" s="3">
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2726,7 +2711,7 @@
         <v>56032</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
@@ -2735,10 +2720,10 @@
         <v>56032</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2746,19 +2731,19 @@
         <v>302</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D25" s="9">
         <v>59002</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2766,19 +2751,19 @@
         <v>302</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D26" s="9">
         <v>59002</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2786,19 +2771,19 @@
         <v>302</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D27" s="9">
         <v>59002</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2806,19 +2791,19 @@
         <v>302</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D28" s="9">
         <v>59002</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2826,19 +2811,19 @@
         <v>302</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D29" s="9">
         <v>59002</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2846,19 +2831,19 @@
         <v>55306</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D30" s="6">
         <v>60768</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G30" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2866,22 +2851,22 @@
         <v>55306</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="D31" s="6">
         <v>60768</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2889,19 +2874,19 @@
         <v>55306</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D32" s="6">
         <v>60768</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2909,22 +2894,22 @@
         <v>55306</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D33" s="6">
         <v>60768</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2932,19 +2917,19 @@
         <v>3006</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D34" s="6">
         <v>55655</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2952,19 +2937,19 @@
         <v>3006</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D35" s="6">
         <v>55655</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G35" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2972,19 +2957,19 @@
         <v>544</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D36" s="6">
         <v>57070</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2992,19 +2977,19 @@
         <v>544</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D37" s="6">
         <v>57070</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3012,19 +2997,19 @@
         <v>544</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D38" s="6">
         <v>57070</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3032,19 +3017,19 @@
         <v>544</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D39" s="6">
         <v>57070</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3052,19 +3037,19 @@
         <v>3176</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D40" s="6">
         <v>3176</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3072,22 +3057,22 @@
         <v>3176</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D41" s="6">
         <v>3176</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3095,19 +3080,19 @@
         <v>3176</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D42" s="6">
         <v>3176</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3115,22 +3100,22 @@
         <v>3176</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D43" s="6">
         <v>3176</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3138,22 +3123,22 @@
         <v>52151</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D44" s="6">
         <v>52151</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3161,22 +3146,22 @@
         <v>52151</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D45" s="6">
         <v>52151</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3184,22 +3169,22 @@
         <v>52151</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D46" s="6">
         <v>52151</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3207,22 +3192,22 @@
         <v>52151</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D47" s="6">
         <v>52151</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3230,22 +3215,22 @@
         <v>1363</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3253,22 +3238,22 @@
         <v>1363</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3276,22 +3261,22 @@
         <v>2398</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3299,22 +3284,22 @@
         <v>2398</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3322,22 +3307,22 @@
         <v>2398</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3345,22 +3330,22 @@
         <v>2398</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3368,19 +3353,19 @@
         <v>7288</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3388,19 +3373,19 @@
         <v>10294</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D55" s="6">
         <v>55811</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3408,22 +3393,22 @@
         <v>50561</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D56" s="6">
         <v>50561</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3431,22 +3416,22 @@
         <v>50561</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D57" s="6">
         <v>50561</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3454,19 +3439,19 @@
         <v>55464</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="D58" s="6">
         <v>55464</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3474,22 +3459,22 @@
         <v>55708</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D59" s="6">
         <v>55708</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3497,19 +3482,19 @@
         <v>56963</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="D60" s="6">
         <v>56963</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3517,19 +3502,19 @@
         <v>56963</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="D61" s="6">
         <v>56963</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3537,19 +3522,19 @@
         <v>57842</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D62" s="6">
         <v>57842</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3557,19 +3542,19 @@
         <v>58503</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D63" s="6">
         <v>58503</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3577,19 +3562,19 @@
         <v>58503</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D64" s="6">
         <v>58503</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3597,19 +3582,19 @@
         <v>63628</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D65" s="6">
         <v>2953</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3617,19 +3602,19 @@
         <v>63628</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D66" s="6">
         <v>2953</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3637,19 +3622,19 @@
         <v>63628</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D67" s="6">
         <v>2953</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3657,19 +3642,19 @@
         <v>63628</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D68" s="6">
         <v>2953</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3677,19 +3662,19 @@
         <v>7909</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3697,19 +3682,19 @@
         <v>7909</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3717,19 +3702,19 @@
         <v>55518</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>387</v>
+        <v>402</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>380</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3737,19 +3722,19 @@
         <v>55518</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3757,19 +3742,19 @@
         <v>56480</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D73" s="6">
         <v>56480</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3777,19 +3762,19 @@
         <v>56480</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D74" s="6">
         <v>56480</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -3815,25 +3800,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3841,15 +3826,15 @@
         <v>1594</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3"/>
       <c r="F2" s="4"/>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3857,15 +3842,15 @@
         <v>1594</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3873,15 +3858,15 @@
         <v>1594</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3889,15 +3874,15 @@
         <v>1594</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3905,15 +3890,15 @@
         <v>1594</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3921,15 +3906,15 @@
         <v>1594</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3937,15 +3922,15 @@
         <v>1594</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3953,15 +3938,15 @@
         <v>1594</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3969,15 +3954,15 @@
         <v>2504</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3985,15 +3970,15 @@
         <v>2504</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4001,15 +3986,15 @@
         <v>2504</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4017,15 +4002,15 @@
         <v>2549</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4033,15 +4018,15 @@
         <v>2549</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4049,15 +4034,15 @@
         <v>10675</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4065,15 +4050,15 @@
         <v>10675</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4081,10 +4066,10 @@
         <v>880004</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4092,10 +4077,10 @@
         <v>880004</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4103,10 +4088,10 @@
         <v>880004</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4114,10 +4099,10 @@
         <v>880004</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4125,13 +4110,13 @@
         <v>880004</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -4139,13 +4124,13 @@
         <v>880004</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -4153,10 +4138,10 @@
         <v>880004</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -4164,10 +4149,10 @@
         <v>880006</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -4175,10 +4160,10 @@
         <v>880006</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -4186,10 +4171,10 @@
         <v>880006</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -4197,10 +4182,10 @@
         <v>880006</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -4208,10 +4193,10 @@
         <v>880007</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -4219,10 +4204,10 @@
         <v>880016</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G29" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -4230,10 +4215,10 @@
         <v>880016</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G30" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -4241,10 +4226,10 @@
         <v>880016</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G31" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -4252,10 +4237,10 @@
         <v>880023</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -4263,10 +4248,10 @@
         <v>880023</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G33" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -4274,10 +4259,10 @@
         <v>880023</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G34" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -4285,10 +4270,10 @@
         <v>880023</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G35" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -4296,10 +4281,10 @@
         <v>880024</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G36" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -4307,10 +4292,10 @@
         <v>880025</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G37" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -4318,10 +4303,10 @@
         <v>880025</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -4329,10 +4314,10 @@
         <v>880025</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G39" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -4340,10 +4325,10 @@
         <v>880025</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G40" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -4351,10 +4336,10 @@
         <v>880028</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G41" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -4362,10 +4347,10 @@
         <v>880029</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G42" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -4373,10 +4358,10 @@
         <v>880030</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G43" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -4384,10 +4369,10 @@
         <v>880030</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G44" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -4395,10 +4380,10 @@
         <v>880031</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G45" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -4406,10 +4391,10 @@
         <v>880031</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G46" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -4417,10 +4402,10 @@
         <v>880033</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G47" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -4428,10 +4413,10 @@
         <v>880038</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G48" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -4439,10 +4424,10 @@
         <v>880039</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G49" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -4450,10 +4435,10 @@
         <v>880039</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G50" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -4461,10 +4446,10 @@
         <v>880041</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -4472,10 +4457,10 @@
         <v>880041</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G52" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -4483,10 +4468,10 @@
         <v>880041</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G53" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4494,10 +4479,10 @@
         <v>880042</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G54" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4505,10 +4490,10 @@
         <v>880042</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G55" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4516,10 +4501,10 @@
         <v>880042</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G56" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4527,10 +4512,10 @@
         <v>880042</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G57" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4538,10 +4523,10 @@
         <v>880043</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4549,10 +4534,10 @@
         <v>880044</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G59" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4560,10 +4545,10 @@
         <v>880045</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G60" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4571,10 +4556,10 @@
         <v>880045</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G61" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4582,10 +4567,10 @@
         <v>880045</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G62" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4593,10 +4578,10 @@
         <v>880049</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G63" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4604,10 +4589,10 @@
         <v>880050</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G64" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4615,10 +4600,10 @@
         <v>880052</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G65" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4626,10 +4611,10 @@
         <v>880053</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G66" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4637,10 +4622,10 @@
         <v>880053</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G67" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4648,10 +4633,10 @@
         <v>880053</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G68" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4659,10 +4644,10 @@
         <v>880053</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G69" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4670,10 +4655,10 @@
         <v>880053</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G70" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4681,10 +4666,10 @@
         <v>880055</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G71" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4692,10 +4677,10 @@
         <v>880055</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G72" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4703,10 +4688,10 @@
         <v>880055</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G73" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4714,10 +4699,10 @@
         <v>880057</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G74" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4725,10 +4710,10 @@
         <v>880057</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G75" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4736,10 +4721,10 @@
         <v>880065</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G76" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4747,10 +4732,10 @@
         <v>880065</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G77" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4758,10 +4743,10 @@
         <v>880067</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4769,10 +4754,10 @@
         <v>880067</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G79" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4780,10 +4765,10 @@
         <v>880067</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G80" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4791,10 +4776,10 @@
         <v>880067</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G81" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4802,10 +4787,10 @@
         <v>880071</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G82" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4813,10 +4798,10 @@
         <v>880072</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G83" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4824,10 +4809,10 @@
         <v>880074</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G84" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4835,10 +4820,10 @@
         <v>880075</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G85" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4846,10 +4831,10 @@
         <v>880075</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G86" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4857,10 +4842,10 @@
         <v>880076</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G87" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4868,10 +4853,10 @@
         <v>880076</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G88" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4879,10 +4864,10 @@
         <v>880076</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G89" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4890,10 +4875,10 @@
         <v>880078</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G90" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4901,10 +4886,10 @@
         <v>880079</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G91" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4912,10 +4897,10 @@
         <v>880079</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G92" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4923,13 +4908,13 @@
         <v>880079</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G93" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4937,13 +4922,13 @@
         <v>880079</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G94" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4951,10 +4936,10 @@
         <v>880083</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G95" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4962,10 +4947,10 @@
         <v>880086</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G96" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4973,10 +4958,10 @@
         <v>880086</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G97" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4984,10 +4969,10 @@
         <v>880086</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G98" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4995,10 +4980,10 @@
         <v>880087</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G99" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5006,10 +4991,10 @@
         <v>880088</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G100" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5017,10 +5002,10 @@
         <v>880088</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G101" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5028,10 +5013,10 @@
         <v>880088</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G102" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5039,10 +5024,10 @@
         <v>880089</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G103" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5050,10 +5035,10 @@
         <v>880092</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G104" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5061,10 +5046,10 @@
         <v>880092</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G105" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5072,10 +5057,10 @@
         <v>880093</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G106" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5083,10 +5068,10 @@
         <v>880093</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G107" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5094,10 +5079,10 @@
         <v>880096</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G108" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5105,10 +5090,10 @@
         <v>880100</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G109" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5116,10 +5101,10 @@
         <v>880100</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G110" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5127,10 +5112,10 @@
         <v>880100</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G111" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5138,10 +5123,10 @@
         <v>880100</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G112" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5149,10 +5134,10 @@
         <v>880101</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G113" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5160,13 +5145,13 @@
         <v>880102</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G114" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5174,13 +5159,13 @@
         <v>880102</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G115" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5188,10 +5173,10 @@
         <v>880107</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G116" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5199,10 +5184,10 @@
         <v>880107</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G117" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5210,10 +5195,10 @@
         <v>880107</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G118" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5221,10 +5206,10 @@
         <v>880107</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G119" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5232,10 +5217,10 @@
         <v>880108</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G120" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5243,10 +5228,10 @@
         <v>880108</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G121" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5254,10 +5239,10 @@
         <v>228</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D122" s="1">
         <v>228</v>
@@ -5269,7 +5254,7 @@
         <v>7</v>
       </c>
       <c r="G122" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5277,10 +5262,10 @@
         <v>228</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D123" s="1">
         <v>228</v>
@@ -5292,7 +5277,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5300,22 +5285,22 @@
         <v>259</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D124" s="3">
         <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G124" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5323,22 +5308,22 @@
         <v>259</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D125" s="3">
         <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G125" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5346,22 +5331,22 @@
         <v>259</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D126" s="3">
         <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G126" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5369,22 +5354,22 @@
         <v>259</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D127" s="3">
         <v>259</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G127" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5392,10 +5377,10 @@
         <v>271</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D128" s="3">
         <v>271</v>
@@ -5407,7 +5392,7 @@
         <v>5</v>
       </c>
       <c r="G128" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5415,10 +5400,10 @@
         <v>271</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D129" s="3">
         <v>271</v>
@@ -5430,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="G129" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5438,10 +5423,10 @@
         <v>271</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D130" s="3">
         <v>271</v>
@@ -5453,7 +5438,7 @@
         <v>7</v>
       </c>
       <c r="G130" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5461,241 +5446,237 @@
         <v>273</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D131" s="3">
         <v>273</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F131" s="1">
         <v>3</v>
       </c>
       <c r="G131" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>310</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D132" s="2">
+        <v>310</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>310</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="2">
+        <v>310</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>356</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>389</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D135" s="2">
+        <v>389</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G135" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="17">
-        <v>310</v>
-      </c>
-      <c r="B132" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C132" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D132" s="17">
-        <v>310</v>
-      </c>
-      <c r="E132" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F132" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="17">
-        <v>310</v>
-      </c>
-      <c r="B133" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C133" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D133" s="17">
-        <v>310</v>
-      </c>
-      <c r="E133" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F133" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="17">
-        <v>356</v>
-      </c>
-      <c r="B134" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C134" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D134" s="18"/>
-      <c r="E134" s="18"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="17">
-        <v>389</v>
-      </c>
-      <c r="B135" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C135" s="18"/>
-      <c r="D135" s="17">
-        <v>389</v>
-      </c>
-      <c r="E135" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F135" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="17" t="s">
+      <c r="A136" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>51000</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="C140" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C136" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D136" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="E136" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="F136" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G136" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D137" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D138" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="B139" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C139" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D139" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="17">
-        <v>51000</v>
-      </c>
-      <c r="B140" s="17" t="s">
+      <c r="F140" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G140" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C140" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>236</v>
-      </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="19">
+      <c r="A141" s="6">
         <v>54571</v>
       </c>
-      <c r="B141" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C141" s="18" t="s">
-        <v>72</v>
+      <c r="B141" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="D141" s="6">
         <v>54571</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5703,19 +5684,19 @@
         <v>54571</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D142" s="6">
         <v>54571</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,19 +5704,19 @@
         <v>54571</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D143" s="6">
         <v>54571</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5743,19 +5724,19 @@
         <v>54571</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D144" s="6">
         <v>54571</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5763,13 +5744,13 @@
         <v>55098</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5777,13 +5758,13 @@
         <v>55098</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5791,13 +5772,13 @@
         <v>55098</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5805,13 +5786,13 @@
         <v>55098</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5819,13 +5800,13 @@
         <v>55524</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -5833,13 +5814,13 @@
         <v>55524</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -5847,13 +5828,13 @@
         <v>55524</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,13 +5842,13 @@
         <v>55524</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5875,13 +5856,13 @@
         <v>55699</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G153" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5889,19 +5870,19 @@
         <v>60345</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D154" s="6">
         <v>60345</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5909,22 +5890,22 @@
         <v>60345</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D155" s="6">
         <v>60345</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5932,19 +5913,19 @@
         <v>60345</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D156" s="6">
         <v>60345</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5952,22 +5933,22 @@
         <v>60345</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D157" s="6">
         <v>60345</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5975,19 +5956,19 @@
         <v>60345</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D158" s="6">
         <v>60345</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5995,22 +5976,22 @@
         <v>60345</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D159" s="6">
         <v>60345</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6018,19 +5999,19 @@
         <v>10803</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D160" s="6">
         <v>10803</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6038,19 +6019,19 @@
         <v>10803</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D161" s="6">
         <v>10803</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -6074,16 +6055,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>3</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6091,13 +6072,13 @@
         <v>330</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C2" s="10">
         <v>57901</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6105,13 +6086,13 @@
         <v>562</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C3" s="10">
         <v>57068</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6119,13 +6100,13 @@
         <v>762</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C4" s="10">
         <v>7546</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6133,13 +6114,13 @@
         <v>1416</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C5" s="10">
         <v>56565</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6147,13 +6128,13 @@
         <v>2709</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C6" s="10">
         <v>58215</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6161,13 +6142,13 @@
         <v>2713</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C7" s="10">
         <v>58697</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -6175,13 +6156,13 @@
         <v>4076</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C8" s="10">
         <v>7799</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6189,13 +6170,13 @@
         <v>7254</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C9" s="10">
         <v>7294</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6203,13 +6184,13 @@
         <v>7258</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C10" s="10">
         <v>7268</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6217,13 +6198,13 @@
         <v>7762</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C11" s="10">
         <v>55545</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -6231,13 +6212,13 @@
         <v>7765</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C12" s="10">
         <v>7709</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -6245,13 +6226,13 @@
         <v>10474</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C13" s="10">
         <v>10397</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -6259,13 +6240,13 @@
         <v>10474</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C14" s="10">
         <v>54995</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -6273,13 +6254,13 @@
         <v>10619</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C15" s="10">
         <v>7784</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6287,13 +6268,13 @@
         <v>50030</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C16" s="10">
         <v>1393</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6301,13 +6282,13 @@
         <v>55120</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C17" s="10">
         <v>10789</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -6315,13 +6296,13 @@
         <v>55306</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C18" s="10">
         <v>59338</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6329,13 +6310,13 @@
         <v>55306</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C19" s="10">
         <v>59784</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6343,13 +6324,13 @@
         <v>55375</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C20" s="10">
         <v>57664</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6357,13 +6338,13 @@
         <v>55481</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C21" s="10">
         <v>58557</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -6371,13 +6352,13 @@
         <v>55508</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C22" s="10">
         <v>55874</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -6385,13 +6366,13 @@
         <v>70454</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C23" s="10">
         <v>54538</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -6399,13 +6380,13 @@
         <v>7146</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C24" s="11">
         <v>2518</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -6430,25 +6411,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6456,10 +6437,10 @@
         <v>1702</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6467,10 +6448,10 @@
         <v>1702</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G3" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6478,7 +6459,7 @@
         <v>2440</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6486,7 +6467,7 @@
         <v>2503</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6494,7 +6475,7 @@
         <v>2503</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6502,7 +6483,7 @@
         <v>2503</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6510,7 +6491,7 @@
         <v>2503</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6518,7 +6499,7 @@
         <v>2503</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6526,7 +6507,7 @@
         <v>2828</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6534,7 +6515,7 @@
         <v>2828</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6542,7 +6523,7 @@
         <v>3148</v>
       </c>
       <c r="B12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6550,7 +6531,7 @@
         <v>3149</v>
       </c>
       <c r="B13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6558,7 +6539,7 @@
         <v>3149</v>
       </c>
       <c r="B14" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6566,7 +6547,7 @@
         <v>3399</v>
       </c>
       <c r="B15" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6574,7 +6555,7 @@
         <v>3399</v>
       </c>
       <c r="B16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -6582,7 +6563,7 @@
         <v>3406</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6590,7 +6571,7 @@
         <v>3406</v>
       </c>
       <c r="B18" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -6598,7 +6579,7 @@
         <v>3935</v>
       </c>
       <c r="B19" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -6606,7 +6587,7 @@
         <v>3935</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -6614,7 +6595,7 @@
         <v>3948</v>
       </c>
       <c r="B21" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -6622,7 +6603,7 @@
         <v>6019</v>
       </c>
       <c r="B22" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -6630,7 +6611,7 @@
         <v>6019</v>
       </c>
       <c r="B23" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -6638,7 +6619,7 @@
         <v>6166</v>
       </c>
       <c r="B24" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -6646,7 +6627,7 @@
         <v>6166</v>
       </c>
       <c r="B25" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -6654,7 +6635,7 @@
         <v>6264</v>
       </c>
       <c r="B26" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -6662,7 +6643,7 @@
         <v>6264</v>
       </c>
       <c r="B27" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -6670,7 +6651,7 @@
         <v>7737</v>
       </c>
       <c r="B28" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -6678,7 +6659,7 @@
         <v>7737</v>
       </c>
       <c r="B29" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -6686,7 +6667,7 @@
         <v>7737</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -6694,7 +6675,7 @@
         <v>8102</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -6702,7 +6683,7 @@
         <v>8102</v>
       </c>
       <c r="B32" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -6710,7 +6691,7 @@
         <v>10474</v>
       </c>
       <c r="B33" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -6718,7 +6699,7 @@
         <v>10474</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -6726,7 +6707,7 @@
         <v>10474</v>
       </c>
       <c r="B35" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -6734,7 +6715,7 @@
         <v>10474</v>
       </c>
       <c r="B36" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -6742,7 +6723,7 @@
         <v>10474</v>
       </c>
       <c r="B37" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -6750,7 +6731,7 @@
         <v>10474</v>
       </c>
       <c r="B38" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -6758,7 +6739,7 @@
         <v>10474</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -6766,7 +6747,7 @@
         <v>10788</v>
       </c>
       <c r="B40" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -6774,7 +6755,7 @@
         <v>10865</v>
       </c>
       <c r="B41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -6782,7 +6763,7 @@
         <v>10865</v>
       </c>
       <c r="B42" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -6790,7 +6771,7 @@
         <v>10866</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -6798,7 +6779,7 @@
         <v>10866</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -6806,7 +6787,7 @@
         <v>10867</v>
       </c>
       <c r="B45" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -6814,7 +6795,7 @@
         <v>10867</v>
       </c>
       <c r="B46" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -6822,7 +6803,7 @@
         <v>50044</v>
       </c>
       <c r="B47" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -6830,7 +6811,7 @@
         <v>50151</v>
       </c>
       <c r="B48" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -6838,7 +6819,7 @@
         <v>50151</v>
       </c>
       <c r="B49" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -6846,7 +6827,7 @@
         <v>50188</v>
       </c>
       <c r="B50" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -6854,7 +6835,7 @@
         <v>50188</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -6862,7 +6843,7 @@
         <v>50240</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -6870,7 +6851,7 @@
         <v>50240</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -6878,7 +6859,7 @@
         <v>50240</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -6886,7 +6867,7 @@
         <v>50240</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -6894,7 +6875,7 @@
         <v>50244</v>
       </c>
       <c r="B56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -6902,7 +6883,7 @@
         <v>50244</v>
       </c>
       <c r="B57" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -6910,7 +6891,7 @@
         <v>50244</v>
       </c>
       <c r="B58" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -6918,7 +6899,7 @@
         <v>50244</v>
       </c>
       <c r="B59" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -6926,7 +6907,7 @@
         <v>50244</v>
       </c>
       <c r="B60" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -6934,7 +6915,7 @@
         <v>50472</v>
       </c>
       <c r="B61" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -6942,7 +6923,7 @@
         <v>50479</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -6950,7 +6931,7 @@
         <v>50481</v>
       </c>
       <c r="B63" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -6958,7 +6939,7 @@
         <v>50607</v>
       </c>
       <c r="B64" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -6966,7 +6947,7 @@
         <v>50607</v>
       </c>
       <c r="B65" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -6974,7 +6955,7 @@
         <v>50607</v>
       </c>
       <c r="B66" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -6982,7 +6963,7 @@
         <v>50607</v>
       </c>
       <c r="B67" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -6990,7 +6971,7 @@
         <v>50607</v>
       </c>
       <c r="B68" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -6998,7 +6979,7 @@
         <v>50627</v>
       </c>
       <c r="B69" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7006,7 +6987,7 @@
         <v>50628</v>
       </c>
       <c r="B70" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7014,7 +6995,7 @@
         <v>50729</v>
       </c>
       <c r="B71" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7022,7 +7003,7 @@
         <v>50729</v>
       </c>
       <c r="B72" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7030,7 +7011,7 @@
         <v>50733</v>
       </c>
       <c r="B73" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7038,7 +7019,7 @@
         <v>50733</v>
       </c>
       <c r="B74" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7046,7 +7027,7 @@
         <v>50733</v>
       </c>
       <c r="B75" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7054,7 +7035,7 @@
         <v>50733</v>
       </c>
       <c r="B76" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7062,7 +7043,7 @@
         <v>50733</v>
       </c>
       <c r="B77" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7070,7 +7051,7 @@
         <v>50733</v>
       </c>
       <c r="B78" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7078,7 +7059,7 @@
         <v>50733</v>
       </c>
       <c r="B79" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7086,7 +7067,7 @@
         <v>50733</v>
       </c>
       <c r="B80" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -7094,7 +7075,7 @@
         <v>50900</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -7102,7 +7083,7 @@
         <v>50900</v>
       </c>
       <c r="B82" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -7110,7 +7091,7 @@
         <v>50900</v>
       </c>
       <c r="B83" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -7118,7 +7099,7 @@
         <v>50900</v>
       </c>
       <c r="B84" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -7126,7 +7107,7 @@
         <v>50956</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -7134,7 +7115,7 @@
         <v>50956</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -7142,7 +7123,7 @@
         <v>50965</v>
       </c>
       <c r="B87" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -7150,7 +7131,7 @@
         <v>50965</v>
       </c>
       <c r="B88" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -7158,7 +7139,7 @@
         <v>50965</v>
       </c>
       <c r="B89" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -7166,7 +7147,7 @@
         <v>52089</v>
       </c>
       <c r="B90" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -7174,7 +7155,7 @@
         <v>52089</v>
       </c>
       <c r="B91" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -7182,7 +7163,7 @@
         <v>52089</v>
       </c>
       <c r="B92" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -7190,7 +7171,7 @@
         <v>52089</v>
       </c>
       <c r="B93" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -7198,7 +7179,7 @@
         <v>52089</v>
       </c>
       <c r="B94" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -7206,7 +7187,7 @@
         <v>52168</v>
       </c>
       <c r="B95" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -7214,7 +7195,7 @@
         <v>52193</v>
       </c>
       <c r="B96" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -7222,7 +7203,7 @@
         <v>52193</v>
       </c>
       <c r="B97" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -7230,7 +7211,7 @@
         <v>52193</v>
       </c>
       <c r="B98" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -7238,7 +7219,7 @@
         <v>52193</v>
       </c>
       <c r="B99" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -7246,7 +7227,7 @@
         <v>52193</v>
       </c>
       <c r="B100" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -7254,7 +7235,7 @@
         <v>52193</v>
       </c>
       <c r="B101" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -7262,7 +7243,7 @@
         <v>52193</v>
       </c>
       <c r="B102" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -7270,7 +7251,7 @@
         <v>52193</v>
       </c>
       <c r="B103" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -7278,7 +7259,7 @@
         <v>54276</v>
       </c>
       <c r="B104" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -7286,7 +7267,7 @@
         <v>55216</v>
       </c>
       <c r="B105" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -7294,7 +7275,7 @@
         <v>55216</v>
       </c>
       <c r="B106" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -7302,7 +7283,7 @@
         <v>55308</v>
       </c>
       <c r="B107" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -7310,7 +7291,7 @@
         <v>55308</v>
       </c>
       <c r="B108" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -7318,7 +7299,7 @@
         <v>55386</v>
       </c>
       <c r="B109" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -7326,7 +7307,7 @@
         <v>55386</v>
       </c>
       <c r="B110" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -7334,7 +7315,7 @@
         <v>55386</v>
       </c>
       <c r="B111" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -7342,7 +7323,7 @@
         <v>55703</v>
       </c>
       <c r="B112" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -7361,39 +7342,39 @@
   <sheetData>
     <row r="1" spans="1:2" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="180" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>370</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="225" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>372</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="330" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>415</v>
@@ -7407,53 +7388,10 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2021-06-22T20:59:33+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF32AD688505FB45A4B74E8374DD655E" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="820e166eda12a2b21727580e35d4b1c4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="03c14dc6-992a-47d3-9648-df74221fc344" xmlns:ns6="434a65cb-19a2-4f64-81f9-c4c3497f5b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73bb20789afc0d8257071bd90159119b" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7890,41 +7828,63 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2021-06-22T20:59:33+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D1F9EA-526B-4162-847E-36B5EC9F2951}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B99ED44-03A6-4635-B387-C99415CE560D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F48335-9609-4D38-B63B-9A6620FE759C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="434a65cb-19a2-4f64-81f9-c4c3497f5b4c"/>
-    <ds:schemaRef ds:uri="03c14dc6-992a-47d3-9648-df74221fc344"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D1E071-1F27-41E0-9A83-EBB1CE4676B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7947,10 +7907,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F48335-9609-4D38-B63B-9A6620FE759C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="434a65cb-19a2-4f64-81f9-c4c3497f5b4c"/>
+    <ds:schemaRef ds:uri="03c14dc6-992a-47d3-9648-df74221fc344"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B99ED44-03A6-4635-B387-C99415CE560D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D1F9EA-526B-4162-847E-36B5EC9F2951}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/manual_matches.xlsx
+++ b/manual_matches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\capd_eia_crosswalk\users\zhangm\camd-eia-crosswalk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\capd_eia_crosswalk\users\gofortht\crosswalk_repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC81CDD0-E737-4305-BC2D-C2CCC8F6CACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45954162-E376-4628-91CD-EACC30ECD91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2370" yWindow="3900" windowWidth="28800" windowHeight="7800" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_manual_matches" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="422">
   <si>
     <t>EIA_PLANT_ID</t>
   </si>
@@ -369,9 +369,6 @@
     <t>Plant ID mismatch, reconciled by searching facility name. This unit is a peaking facility. Cogen: https://www.calpine.com/Operations/Power-Operations/Our-Fleet/California/King-City-Cogeneration-Plant, Peaking: https://www.calpine.com/king-city-peaking-energy-center</t>
   </si>
   <si>
-    <t>Unit retired in 2007, still listed as operating in CAMD database. Match verified using the Retired tab of the EIA-860.</t>
-  </si>
-  <si>
     <t>STG4</t>
   </si>
   <si>
@@ -705,9 +702,6 @@
     <t>Unit missing from EIA-860; Unit 17 is an auxiliary boiler that retired at the end of 2018; https://www.transmissionhub.com/articles/2012/12/california-staff-reviews-early-aes-redondo-beach-application.html</t>
   </si>
   <si>
-    <t>Generator is missing from CAMD, but shows up in EIA-860 2018 retired sheet</t>
-  </si>
-  <si>
     <t>VB01</t>
   </si>
   <si>
@@ -741,9 +735,6 @@
     <t>CFB1</t>
   </si>
   <si>
-    <t>Unit retired in 2010 according to EIA-860 2010. See EIA-860 2010. No reported emissions in CAMD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unit retired in 2010 according to EIA-860 2010. See EIA-860 2010. </t>
   </si>
   <si>
@@ -1161,9 +1152,6 @@
     <t>STG3</t>
   </si>
   <si>
-    <t>Unit began operating in 2019 (even though it shows up in CAMD's database in 2018).</t>
-  </si>
-  <si>
     <t>Unit is missing from EIA-860, but exists according to this permit: https://www.dec.ny.gov/dardata/boss/afs/permits/prr_263080051300012_r2.pdf</t>
   </si>
   <si>
@@ -1288,6 +1276,36 @@
   </si>
   <si>
     <t>These units exist in EPA without a generator ID. They are likely industrial units and not in the EIA database, but we welcome research or information on these units</t>
+  </si>
+  <si>
+    <t>Generator is missing from EPA, but shows up in EIA-860 2018 retired sheet</t>
+  </si>
+  <si>
+    <t>Unit retired in 2010 according to EIA-860 2010. See EIA-860 2010. No reported emissions in EPA</t>
+  </si>
+  <si>
+    <t>Unit began operating in 2019 (even though it shows up in EPA's database in 2018).</t>
+  </si>
+  <si>
+    <t>Unit retired in 2007, still listed as operating in EPA database. Match verified using the Retired tab of the EIA-860.</t>
+  </si>
+  <si>
+    <t>BLR01A</t>
+  </si>
+  <si>
+    <t>BLR01B</t>
+  </si>
+  <si>
+    <t>BLR01C</t>
+  </si>
+  <si>
+    <t>BLR02A</t>
+  </si>
+  <si>
+    <t>BLR02B</t>
+  </si>
+  <si>
+    <t>BLR02C</t>
   </si>
 </sst>
 </file>
@@ -2209,13 +2227,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
@@ -2250,7 +2268,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2273,7 +2291,7 @@
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2296,7 +2314,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2319,7 +2337,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2342,7 +2360,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2365,7 +2383,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2388,7 +2406,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2411,7 +2429,7 @@
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2434,7 +2452,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2631,7 +2649,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D20" s="6">
         <v>7903</v>
@@ -2640,7 +2658,7 @@
         <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2651,7 +2669,7 @@
         <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D21" s="6">
         <v>7903</v>
@@ -2660,7 +2678,7 @@
         <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3365,7 +3383,7 @@
         <v>106</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3396,7 +3414,7 @@
         <v>40</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D56" s="6">
         <v>50561</v>
@@ -3405,10 +3423,10 @@
         <v>40</v>
       </c>
       <c r="F56" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3416,22 +3434,22 @@
         <v>50561</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D57" s="6">
         <v>50561</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F57" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3439,19 +3457,19 @@
         <v>55464</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D58" s="6">
         <v>55464</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3459,22 +3477,22 @@
         <v>55708</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D59" s="6">
         <v>55708</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3482,19 +3500,19 @@
         <v>56963</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D60" s="6">
         <v>56963</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3502,19 +3520,19 @@
         <v>56963</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D61" s="6">
         <v>56963</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3525,7 +3543,7 @@
         <v>15</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D62" s="6">
         <v>57842</v>
@@ -3534,7 +3552,7 @@
         <v>6</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3542,10 +3560,10 @@
         <v>58503</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D63" s="6">
         <v>58503</v>
@@ -3554,7 +3572,7 @@
         <v>69</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3562,7 +3580,7 @@
         <v>58503</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>11</v>
@@ -3574,7 +3592,7 @@
         <v>71</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3582,19 +3600,19 @@
         <v>63628</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D65" s="6">
         <v>2953</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3602,19 +3620,19 @@
         <v>63628</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D66" s="6">
         <v>2953</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3622,19 +3640,19 @@
         <v>63628</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D67" s="6">
         <v>2953</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3642,19 +3660,19 @@
         <v>63628</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D68" s="6">
         <v>2953</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3662,19 +3680,19 @@
         <v>7909</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="G69" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3682,19 +3700,19 @@
         <v>7909</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="G70" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3705,16 +3723,16 @@
         <v>34</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3725,16 +3743,16 @@
         <v>62</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3751,10 +3769,10 @@
         <v>56480</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3771,10 +3789,10 @@
         <v>56480</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -3787,7 +3805,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" style="6" bestFit="1" customWidth="1"/>
@@ -3800,13 +3818,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -3822,2220 +3840,2598 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
+        <v>228</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="1">
+        <v>228</v>
+      </c>
+      <c r="E2" s="1">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>228</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="1">
+        <v>228</v>
+      </c>
+      <c r="E3" s="1">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>259</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3">
+        <v>259</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>259</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3">
+        <v>259</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>259</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>259</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>259</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3">
+        <v>259</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>271</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3">
+        <v>271</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>271</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="3">
+        <v>271</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>271</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3">
+        <v>271</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>273</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>273</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>310</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2">
+        <v>310</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>310</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2">
+        <v>310</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>356</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>389</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2">
+        <v>389</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
         <v>1594</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="G2" t="s">
+      <c r="D16" s="3"/>
+      <c r="F16" s="4"/>
+      <c r="G16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>1594</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="F17" s="4"/>
+      <c r="G17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>1594</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>1594</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>1594</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>1594</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>1594</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>1594</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>2440</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="G24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>2504</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="G3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="D25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>2504</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="D26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>2504</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="D27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>2549</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="C28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
         <v>2549</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>2549</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>10071</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>10071</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>10071</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>10071</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>10071</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>10071</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>10675</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="C36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
         <v>10675</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <v>10675</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G22" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>880006</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
-        <v>880006</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>880006</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>880006</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>880007</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>880016</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>880016</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>880016</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G31" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>880023</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G32" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>880023</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G33" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>880023</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>880023</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>880024</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G36" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>880025</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="D37" s="3"/>
+      <c r="F37" s="3"/>
       <c r="G37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>880025</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="A38" s="2">
+        <v>10788</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="G38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>880025</v>
+        <v>10803</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G39" t="s">
-        <v>114</v>
+        <v>15</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="6">
+        <v>10803</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>880025</v>
+        <v>10803</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G40" t="s">
-        <v>114</v>
+        <v>17</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="6">
+        <v>10803</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>880028</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>141</v>
-      </c>
+      <c r="A41" s="2">
+        <v>50044</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="G41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>880029</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>113</v>
+      <c r="A42" s="2">
+        <v>50151</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="G42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>880030</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>142</v>
+      <c r="A43" s="2">
+        <v>50151</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="G43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>880030</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>143</v>
+      <c r="A44" s="2">
+        <v>50202</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="G44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>880031</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>144</v>
-      </c>
+      <c r="A45" s="2">
+        <v>50607</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="G45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
-        <v>880031</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>145</v>
-      </c>
+      <c r="A46" s="2">
+        <v>50607</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="G46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>880033</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>146</v>
-      </c>
+      <c r="A47" s="2">
+        <v>50607</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="G47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>880038</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="A48" s="2">
+        <v>50607</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="G48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>880039</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="A49" s="2">
+        <v>50607</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="G49" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
-        <v>880039</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G50" t="s">
-        <v>114</v>
+      <c r="A50" s="2">
+        <v>51000</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>880041</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>150</v>
+      <c r="A51" s="2">
+        <v>54035</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="G51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>880041</v>
+        <v>54571</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G52" t="s">
-        <v>114</v>
+        <v>85</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" s="6">
+        <v>54571</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>880041</v>
+        <v>54571</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G53" t="s">
-        <v>114</v>
+        <v>85</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D53" s="6">
+        <v>54571</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>880042</v>
+        <v>54571</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G54" t="s">
-        <v>114</v>
+        <v>233</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="6">
+        <v>54571</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>880042</v>
+        <v>54571</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G55" t="s">
-        <v>114</v>
+        <v>233</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D55" s="6">
+        <v>54571</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>880042</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>155</v>
+      <c r="A56" s="2">
+        <v>54571</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>880042</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>156</v>
+      <c r="A57" s="2">
+        <v>54571</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="G57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>880043</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>15</v>
+      <c r="A58" s="2">
+        <v>54571</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="G58" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>880044</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>157</v>
+      <c r="A59" s="2">
+        <v>54571</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="G59" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>880045</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>158</v>
+      <c r="A60" s="2">
+        <v>54755</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="G60" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>880045</v>
+        <v>55098</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G61" t="s">
-        <v>114</v>
+        <v>15</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>880045</v>
+        <v>55098</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G62" t="s">
-        <v>114</v>
+        <v>15</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>880049</v>
+        <v>55098</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G63" t="s">
-        <v>114</v>
+        <v>17</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>880050</v>
+        <v>55098</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G64" t="s">
-        <v>114</v>
+        <v>17</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
-        <v>880052</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>163</v>
+      <c r="A65" s="2">
+        <v>55098</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="G65" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
-        <v>880053</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>164</v>
+      <c r="A66" s="2">
+        <v>55098</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="G66" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
-        <v>880053</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>165</v>
+      <c r="A67" s="2">
+        <v>55098</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="G67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
-        <v>880053</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>166</v>
+      <c r="A68" s="2">
+        <v>55098</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="G68" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>880053</v>
+        <v>55524</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G69" t="s">
-        <v>114</v>
+        <v>30</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>880053</v>
+        <v>55524</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G70" t="s">
-        <v>114</v>
+        <v>30</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>880055</v>
+        <v>55524</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G71" t="s">
-        <v>114</v>
+        <v>44</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>880055</v>
+        <v>55524</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" t="s">
-        <v>114</v>
+        <v>44</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>880055</v>
+        <v>55699</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>170</v>
+        <v>17</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G73" t="s">
-        <v>114</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
-        <v>880057</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>171</v>
-      </c>
+      <c r="A74" s="2">
+        <v>55703</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="G74" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>880057</v>
+        <v>60345</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G75" t="s">
-        <v>114</v>
+        <v>379</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="6">
+        <v>60345</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>880065</v>
+        <v>60345</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G76" t="s">
-        <v>114</v>
+        <v>379</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D76" s="6">
+        <v>60345</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>880065</v>
+        <v>60345</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>114</v>
+        <v>381</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="6">
+        <v>60345</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>880067</v>
+        <v>60345</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>114</v>
+        <v>381</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D78" s="6">
+        <v>60345</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>880067</v>
+        <v>60345</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G79" t="s">
-        <v>114</v>
+        <v>382</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D79" s="6">
+        <v>60345</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>880067</v>
+        <v>60345</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G80" t="s">
-        <v>114</v>
+        <v>382</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D80" s="6">
+        <v>60345</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>880067</v>
+        <v>880004</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>178</v>
+        <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>880071</v>
+        <v>880004</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="G82" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>880072</v>
+        <v>880004</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="G83" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>880074</v>
+        <v>880004</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>880075</v>
+        <v>880004</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>181</v>
+        <v>124</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="G85" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>880075</v>
+        <v>880004</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>182</v>
+        <v>124</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="G86" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>880076</v>
+        <v>880004</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="G87" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>880076</v>
+        <v>880006</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>184</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>880076</v>
+        <v>880006</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="G89" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>880078</v>
+        <v>880006</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="G90" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>880079</v>
+        <v>880006</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>170</v>
+        <v>4</v>
       </c>
       <c r="G91" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>880079</v>
+        <v>880007</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>187</v>
+        <v>127</v>
       </c>
       <c r="G92" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>880079</v>
+        <v>880016</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="G93" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>880079</v>
+        <v>880016</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="G94" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>880083</v>
+        <v>880016</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G95" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>880086</v>
+        <v>880023</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="G96" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>880086</v>
+        <v>880023</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="G97" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>880086</v>
+        <v>880023</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="G98" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>880087</v>
+        <v>880023</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="G99" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>880088</v>
+        <v>880024</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>194</v>
+        <v>135</v>
       </c>
       <c r="G100" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>880088</v>
+        <v>880025</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>195</v>
+        <v>136</v>
       </c>
       <c r="G101" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>880088</v>
+        <v>880025</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="G102" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>880089</v>
+        <v>880025</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="G103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>880092</v>
+        <v>880025</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="G104" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>880092</v>
+        <v>880028</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="G105" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>880093</v>
+        <v>880029</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="G106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>880093</v>
+        <v>880030</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="G107" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>880096</v>
+        <v>880030</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="G108" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>880100</v>
+        <v>880031</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="G109" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>880100</v>
+        <v>880031</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="G110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>880100</v>
+        <v>880033</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="G111" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>880100</v>
+        <v>880038</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="G112" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>880101</v>
+        <v>880039</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>207</v>
+        <v>147</v>
       </c>
       <c r="G113" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>880102</v>
+        <v>880039</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="G114" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>880102</v>
+        <v>880041</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="G115" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>880107</v>
+        <v>880041</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="G116" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>880107</v>
+        <v>880041</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="G117" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>880107</v>
+        <v>880042</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="G118" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>880107</v>
+        <v>880042</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="G119" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>880108</v>
+        <v>880042</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="G120" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>880108</v>
+        <v>880042</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="G121" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>228</v>
+        <v>880043</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D122" s="1">
-        <v>228</v>
-      </c>
-      <c r="E122" s="1">
-        <v>10</v>
-      </c>
-      <c r="F122" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>228</v>
+        <v>880044</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D123" s="1">
-        <v>228</v>
-      </c>
-      <c r="E123" s="1">
-        <v>9</v>
-      </c>
-      <c r="F123" s="1">
-        <v>6</v>
+        <v>156</v>
       </c>
       <c r="G123" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>259</v>
+        <v>880045</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D124" s="3">
-        <v>259</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="G124" t="s">
-        <v>215</v>
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
-        <v>259</v>
+        <v>880045</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D125" s="3">
-        <v>259</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="G125" t="s">
-        <v>215</v>
+        <v>113</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
-        <v>259</v>
+        <v>880045</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D126" s="3">
-        <v>259</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="G126" t="s">
-        <v>215</v>
+        <v>113</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
-        <v>259</v>
+        <v>880049</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D127" s="3">
-        <v>259</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="G127" t="s">
-        <v>215</v>
+        <v>113</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
-        <v>271</v>
+        <v>880050</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D128" s="3">
-        <v>271</v>
-      </c>
-      <c r="E128" s="1">
-        <v>5</v>
-      </c>
-      <c r="F128" s="1">
-        <v>5</v>
+        <v>161</v>
       </c>
       <c r="G128" t="s">
-        <v>216</v>
+        <v>113</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
-        <v>271</v>
+        <v>880052</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D129" s="3">
-        <v>271</v>
-      </c>
-      <c r="E129" s="1">
-        <v>6</v>
-      </c>
-      <c r="F129" s="1">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="G129" t="s">
-        <v>216</v>
+        <v>113</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
-        <v>271</v>
+        <v>880053</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D130" s="3">
-        <v>271</v>
-      </c>
-      <c r="E130" s="1">
-        <v>7</v>
-      </c>
-      <c r="F130" s="1">
-        <v>7</v>
+        <v>163</v>
       </c>
       <c r="G130" t="s">
-        <v>216</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
-        <v>273</v>
+        <v>880053</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D131" s="3">
-        <v>273</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F131" s="1">
-        <v>3</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>218</v>
+        <v>164</v>
+      </c>
+      <c r="G131" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
-        <v>310</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D132" s="2">
-        <v>310</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>219</v>
+      <c r="A132" s="6">
+        <v>880053</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G132" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
-        <v>310</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D133" s="2">
-        <v>310</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>219</v>
+      <c r="A133" s="6">
+        <v>880053</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G133" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
-        <v>356</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>220</v>
+      <c r="A134" s="6">
+        <v>880053</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G134" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
-        <v>389</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D135" s="2">
-        <v>389</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>221</v>
+      <c r="A135" s="6">
+        <v>880055</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G135" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>229</v>
+      <c r="A136" s="6">
+        <v>880055</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
-        <v>227</v>
+      <c r="A137" s="6">
+        <v>880055</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>229</v>
+        <v>169</v>
+      </c>
+      <c r="G137" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
-        <v>227</v>
+      <c r="A138" s="6">
+        <v>880057</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>229</v>
+        <v>170</v>
+      </c>
+      <c r="G138" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
-        <v>227</v>
+      <c r="A139" s="6">
+        <v>880057</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>229</v>
+        <v>171</v>
+      </c>
+      <c r="G139" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>51000</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>233</v>
+      <c r="A140" s="6">
+        <v>880065</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G140" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
-        <v>54571</v>
+        <v>880065</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D141" s="6">
-        <v>54571</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>234</v>
+        <v>173</v>
+      </c>
+      <c r="G141" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>54571</v>
+        <v>880067</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D142" s="6">
-        <v>54571</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>234</v>
+        <v>174</v>
+      </c>
+      <c r="G142" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
-        <v>54571</v>
+        <v>880067</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D143" s="6">
-        <v>54571</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>234</v>
+        <v>175</v>
+      </c>
+      <c r="G143" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>54571</v>
+        <v>880067</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D144" s="6">
-        <v>54571</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>234</v>
+        <v>176</v>
+      </c>
+      <c r="G144" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
-        <v>55098</v>
+        <v>880067</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>368</v>
+        <v>177</v>
+      </c>
+      <c r="G145" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>55098</v>
+        <v>880071</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>368</v>
+        <v>178</v>
+      </c>
+      <c r="G146" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>55098</v>
+        <v>880072</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>368</v>
+        <v>179</v>
+      </c>
+      <c r="G147" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>55098</v>
+        <v>880074</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>368</v>
+        <v>72</v>
+      </c>
+      <c r="G148" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>55524</v>
+        <v>880075</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>373</v>
+        <v>180</v>
+      </c>
+      <c r="G149" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>55524</v>
+        <v>880075</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>373</v>
+        <v>181</v>
+      </c>
+      <c r="G150" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>55524</v>
+        <v>880076</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>373</v>
+        <v>182</v>
+      </c>
+      <c r="G151" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
-        <v>55524</v>
+        <v>880076</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>373</v>
+        <v>183</v>
+      </c>
+      <c r="G152" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
-        <v>55699</v>
+        <v>880076</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>17</v>
+        <v>184</v>
       </c>
       <c r="G153" t="s">
-        <v>374</v>
+        <v>113</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
-        <v>60345</v>
+        <v>880078</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D154" s="6">
-        <v>60345</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>373</v>
+        <v>185</v>
+      </c>
+      <c r="G154" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
-        <v>60345</v>
+        <v>880079</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D155" s="6">
-        <v>60345</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>373</v>
+        <v>169</v>
+      </c>
+      <c r="G155" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
-        <v>60345</v>
+        <v>880079</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D156" s="6">
-        <v>60345</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>373</v>
+        <v>186</v>
+      </c>
+      <c r="G156" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
-        <v>60345</v>
+        <v>880079</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>385</v>
+        <v>187</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D157" s="6">
-        <v>60345</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>373</v>
+        <v>187</v>
+      </c>
+      <c r="G157" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
-        <v>60345</v>
+        <v>880079</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>386</v>
+        <v>188</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D158" s="6">
-        <v>60345</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>373</v>
+        <v>188</v>
+      </c>
+      <c r="G158" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
-        <v>60345</v>
+        <v>880083</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D159" s="6">
-        <v>60345</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>373</v>
+        <v>146</v>
+      </c>
+      <c r="G159" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
-        <v>10803</v>
+        <v>880086</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D160" s="6">
-        <v>10803</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>109</v>
+        <v>189</v>
+      </c>
+      <c r="G160" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
-        <v>10803</v>
+        <v>880086</v>
       </c>
       <c r="B161" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G161" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>880086</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G162" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>880087</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G163" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="6">
+        <v>880088</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G164" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="6">
+        <v>880088</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G165" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="6">
+        <v>880088</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G166" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="6">
+        <v>880089</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G167" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="6">
+        <v>880092</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G168" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="6">
+        <v>880092</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G169" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>880093</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G170" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="6">
+        <v>880093</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G171" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="6">
+        <v>880096</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G172" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="6">
+        <v>880100</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G173" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="6">
+        <v>880100</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G174" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="6">
+        <v>880100</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G175" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="6">
+        <v>880100</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G176" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="6">
+        <v>880101</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G177" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="6">
+        <v>880102</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G178" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="6">
+        <v>880102</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D161" s="6">
-        <v>10803</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>109</v>
+      <c r="C179" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G179" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="6">
+        <v>880107</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G180" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="6">
+        <v>880107</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G181" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="6">
+        <v>880107</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G182" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="6">
+        <v>880107</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G183" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="6">
+        <v>880108</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G184" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="6">
+        <v>880108</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G185" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{C5B36CAD-FD0A-4B42-A5F0-CEDAE9F551CA}"/>
+  <autoFilter ref="A1:G1" xr:uid="{C5B36CAD-FD0A-4B42-A5F0-CEDAE9F551CA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G189">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6055,16 +6451,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6072,13 +6468,13 @@
         <v>330</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C2" s="10">
         <v>57901</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6086,13 +6482,13 @@
         <v>562</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C3" s="10">
         <v>57068</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6100,13 +6496,13 @@
         <v>762</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C4" s="10">
         <v>7546</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6114,13 +6510,13 @@
         <v>1416</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C5" s="10">
         <v>56565</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6128,13 +6524,13 @@
         <v>2709</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C6" s="10">
         <v>58215</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6142,13 +6538,13 @@
         <v>2713</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C7" s="10">
         <v>58697</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -6156,13 +6552,13 @@
         <v>4076</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C8" s="10">
         <v>7799</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6170,13 +6566,13 @@
         <v>7254</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C9" s="10">
         <v>7294</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6184,13 +6580,13 @@
         <v>7258</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C10" s="10">
         <v>7268</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6198,13 +6594,13 @@
         <v>7762</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C11" s="10">
         <v>55545</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -6212,13 +6608,13 @@
         <v>7765</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C12" s="10">
         <v>7709</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -6226,13 +6622,13 @@
         <v>10474</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C13" s="10">
         <v>10397</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -6240,13 +6636,13 @@
         <v>10474</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C14" s="10">
         <v>54995</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -6254,13 +6650,13 @@
         <v>10619</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C15" s="10">
         <v>7784</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6268,13 +6664,13 @@
         <v>50030</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C16" s="10">
         <v>1393</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6282,13 +6678,13 @@
         <v>55120</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C17" s="10">
         <v>10789</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -6296,13 +6692,13 @@
         <v>55306</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C18" s="10">
         <v>59338</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6310,13 +6706,13 @@
         <v>55306</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C19" s="10">
         <v>59784</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6324,13 +6720,13 @@
         <v>55375</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C20" s="10">
         <v>57664</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6338,13 +6734,13 @@
         <v>55481</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C21" s="10">
         <v>58557</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -6352,13 +6748,13 @@
         <v>55508</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C22" s="10">
         <v>55874</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -6366,13 +6762,13 @@
         <v>70454</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C23" s="10">
         <v>54538</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -6380,13 +6776,13 @@
         <v>7146</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C24" s="11">
         <v>2518</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -6411,13 +6807,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -6437,10 +6833,10 @@
         <v>1702</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6448,10 +6844,10 @@
         <v>1702</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6467,7 +6863,7 @@
         <v>2503</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6475,7 +6871,7 @@
         <v>2503</v>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6483,7 +6879,7 @@
         <v>2503</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6491,7 +6887,7 @@
         <v>2503</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6499,7 +6895,7 @@
         <v>2503</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6507,7 +6903,7 @@
         <v>2828</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6515,7 +6911,7 @@
         <v>2828</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6523,7 +6919,7 @@
         <v>3148</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6531,7 +6927,7 @@
         <v>3149</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6539,7 +6935,7 @@
         <v>3149</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6547,7 +6943,7 @@
         <v>3399</v>
       </c>
       <c r="B15" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6555,7 +6951,7 @@
         <v>3399</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -6563,7 +6959,7 @@
         <v>3406</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6571,7 +6967,7 @@
         <v>3406</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -6579,7 +6975,7 @@
         <v>3935</v>
       </c>
       <c r="B19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -6587,7 +6983,7 @@
         <v>3935</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -6595,7 +6991,7 @@
         <v>3948</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -6603,7 +6999,7 @@
         <v>6019</v>
       </c>
       <c r="B22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -6611,7 +7007,7 @@
         <v>6019</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -6619,7 +7015,7 @@
         <v>6166</v>
       </c>
       <c r="B24" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -6627,7 +7023,7 @@
         <v>6166</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -6635,7 +7031,7 @@
         <v>6264</v>
       </c>
       <c r="B26" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -6643,7 +7039,7 @@
         <v>6264</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -6651,7 +7047,7 @@
         <v>7737</v>
       </c>
       <c r="B28" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -6659,7 +7055,7 @@
         <v>7737</v>
       </c>
       <c r="B29" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -6667,7 +7063,7 @@
         <v>7737</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -6675,7 +7071,7 @@
         <v>8102</v>
       </c>
       <c r="B31" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -6683,7 +7079,7 @@
         <v>8102</v>
       </c>
       <c r="B32" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -6691,7 +7087,7 @@
         <v>10474</v>
       </c>
       <c r="B33" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -6699,7 +7095,7 @@
         <v>10474</v>
       </c>
       <c r="B34" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -6707,7 +7103,7 @@
         <v>10474</v>
       </c>
       <c r="B35" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -6715,7 +7111,7 @@
         <v>10474</v>
       </c>
       <c r="B36" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -6723,7 +7119,7 @@
         <v>10474</v>
       </c>
       <c r="B37" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -6731,7 +7127,7 @@
         <v>10474</v>
       </c>
       <c r="B38" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -6739,7 +7135,7 @@
         <v>10474</v>
       </c>
       <c r="B39" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -6747,7 +7143,7 @@
         <v>10788</v>
       </c>
       <c r="B40" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -6755,7 +7151,7 @@
         <v>10865</v>
       </c>
       <c r="B41" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -6763,7 +7159,7 @@
         <v>10865</v>
       </c>
       <c r="B42" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -6787,7 +7183,7 @@
         <v>10867</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -6795,7 +7191,7 @@
         <v>10867</v>
       </c>
       <c r="B46" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -6803,7 +7199,7 @@
         <v>50044</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -6811,7 +7207,7 @@
         <v>50151</v>
       </c>
       <c r="B48" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -6819,7 +7215,7 @@
         <v>50151</v>
       </c>
       <c r="B49" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -6827,7 +7223,7 @@
         <v>50188</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -6875,7 +7271,7 @@
         <v>50244</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -6883,7 +7279,7 @@
         <v>50244</v>
       </c>
       <c r="B57" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -6891,7 +7287,7 @@
         <v>50244</v>
       </c>
       <c r="B58" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -6899,7 +7295,7 @@
         <v>50244</v>
       </c>
       <c r="B59" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -6907,7 +7303,7 @@
         <v>50244</v>
       </c>
       <c r="B60" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -6915,7 +7311,7 @@
         <v>50472</v>
       </c>
       <c r="B61" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -6931,7 +7327,7 @@
         <v>50481</v>
       </c>
       <c r="B63" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -6939,7 +7335,7 @@
         <v>50607</v>
       </c>
       <c r="B64" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -6947,7 +7343,7 @@
         <v>50607</v>
       </c>
       <c r="B65" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -6955,7 +7351,7 @@
         <v>50607</v>
       </c>
       <c r="B66" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -6963,7 +7359,7 @@
         <v>50607</v>
       </c>
       <c r="B67" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -6971,7 +7367,7 @@
         <v>50607</v>
       </c>
       <c r="B68" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -6979,7 +7375,7 @@
         <v>50627</v>
       </c>
       <c r="B69" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -6987,7 +7383,7 @@
         <v>50628</v>
       </c>
       <c r="B70" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -6995,7 +7391,7 @@
         <v>50729</v>
       </c>
       <c r="B71" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7003,7 +7399,7 @@
         <v>50729</v>
       </c>
       <c r="B72" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7011,7 +7407,7 @@
         <v>50733</v>
       </c>
       <c r="B73" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7019,7 +7415,7 @@
         <v>50733</v>
       </c>
       <c r="B74" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7027,7 +7423,7 @@
         <v>50733</v>
       </c>
       <c r="B75" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7035,7 +7431,7 @@
         <v>50733</v>
       </c>
       <c r="B76" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7043,7 +7439,7 @@
         <v>50733</v>
       </c>
       <c r="B77" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7051,7 +7447,7 @@
         <v>50733</v>
       </c>
       <c r="B78" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7059,7 +7455,7 @@
         <v>50733</v>
       </c>
       <c r="B79" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7067,7 +7463,7 @@
         <v>50733</v>
       </c>
       <c r="B80" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -7083,7 +7479,7 @@
         <v>50900</v>
       </c>
       <c r="B82" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -7091,7 +7487,7 @@
         <v>50900</v>
       </c>
       <c r="B83" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -7099,7 +7495,7 @@
         <v>50900</v>
       </c>
       <c r="B84" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -7123,7 +7519,7 @@
         <v>50965</v>
       </c>
       <c r="B87" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -7131,7 +7527,7 @@
         <v>50965</v>
       </c>
       <c r="B88" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -7139,7 +7535,7 @@
         <v>50965</v>
       </c>
       <c r="B89" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -7147,7 +7543,7 @@
         <v>52089</v>
       </c>
       <c r="B90" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -7155,7 +7551,7 @@
         <v>52089</v>
       </c>
       <c r="B91" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -7163,7 +7559,7 @@
         <v>52089</v>
       </c>
       <c r="B92" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -7171,7 +7567,7 @@
         <v>52089</v>
       </c>
       <c r="B93" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -7179,7 +7575,7 @@
         <v>52089</v>
       </c>
       <c r="B94" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -7187,7 +7583,7 @@
         <v>52168</v>
       </c>
       <c r="B95" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -7195,7 +7591,7 @@
         <v>52193</v>
       </c>
       <c r="B96" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -7203,7 +7599,7 @@
         <v>52193</v>
       </c>
       <c r="B97" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -7211,7 +7607,7 @@
         <v>52193</v>
       </c>
       <c r="B98" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -7219,7 +7615,7 @@
         <v>52193</v>
       </c>
       <c r="B99" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -7227,7 +7623,7 @@
         <v>52193</v>
       </c>
       <c r="B100" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -7235,7 +7631,7 @@
         <v>52193</v>
       </c>
       <c r="B101" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -7243,7 +7639,7 @@
         <v>52193</v>
       </c>
       <c r="B102" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -7251,7 +7647,7 @@
         <v>52193</v>
       </c>
       <c r="B103" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -7259,7 +7655,7 @@
         <v>54276</v>
       </c>
       <c r="B104" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -7267,7 +7663,7 @@
         <v>55216</v>
       </c>
       <c r="B105" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -7275,7 +7671,7 @@
         <v>55216</v>
       </c>
       <c r="B106" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -7283,7 +7679,7 @@
         <v>55308</v>
       </c>
       <c r="B107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -7291,7 +7687,7 @@
         <v>55308</v>
       </c>
       <c r="B108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -7299,7 +7695,7 @@
         <v>55386</v>
       </c>
       <c r="B109" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -7307,7 +7703,7 @@
         <v>55386</v>
       </c>
       <c r="B110" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -7315,7 +7711,7 @@
         <v>55386</v>
       </c>
       <c r="B111" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -7323,7 +7719,7 @@
         <v>55703</v>
       </c>
       <c r="B112" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -7337,47 +7733,47 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="82.7109375" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B3" s="13" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="180" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="225" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="330" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>367</v>
-      </c>
       <c r="B4" s="13" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>

--- a/manual_matches.xlsx
+++ b/manual_matches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\capd_eia_crosswalk\users\zhangm\camd-eia-crosswalk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\capd_eia_crosswalk\users\gofortht\crosswalk_repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC81CDD0-E737-4305-BC2D-C2CCC8F6CACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94E93B8-E055-4CA7-BC07-E057045814CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5460" yWindow="1170" windowWidth="28800" windowHeight="7800" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_manual_matches" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">plant_id_manual_matches!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">unit_manual_excluded!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">unit_manual_excluded!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">unit_manual_matches!$A$1:$G$74</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="497">
   <si>
     <t>EIA_PLANT_ID</t>
   </si>
@@ -369,9 +369,6 @@
     <t>Plant ID mismatch, reconciled by searching facility name. This unit is a peaking facility. Cogen: https://www.calpine.com/Operations/Power-Operations/Our-Fleet/California/King-City-Cogeneration-Plant, Peaking: https://www.calpine.com/king-city-peaking-energy-center</t>
   </si>
   <si>
-    <t>Unit retired in 2007, still listed as operating in CAMD database. Match verified using the Retired tab of the EIA-860.</t>
-  </si>
-  <si>
     <t>STG4</t>
   </si>
   <si>
@@ -705,9 +702,6 @@
     <t>Unit missing from EIA-860; Unit 17 is an auxiliary boiler that retired at the end of 2018; https://www.transmissionhub.com/articles/2012/12/california-staff-reviews-early-aes-redondo-beach-application.html</t>
   </si>
   <si>
-    <t>Generator is missing from CAMD, but shows up in EIA-860 2018 retired sheet</t>
-  </si>
-  <si>
     <t>VB01</t>
   </si>
   <si>
@@ -741,9 +735,6 @@
     <t>CFB1</t>
   </si>
   <si>
-    <t>Unit retired in 2010 according to EIA-860 2010. See EIA-860 2010. No reported emissions in CAMD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unit retired in 2010 according to EIA-860 2010. See EIA-860 2010. </t>
   </si>
   <si>
@@ -1161,9 +1152,6 @@
     <t>STG3</t>
   </si>
   <si>
-    <t>Unit began operating in 2019 (even though it shows up in CAMD's database in 2018).</t>
-  </si>
-  <si>
     <t>Unit is missing from EIA-860, but exists according to this permit: https://www.dec.ny.gov/dardata/boss/afs/permits/prr_263080051300012_r2.pdf</t>
   </si>
   <si>
@@ -1288,6 +1276,261 @@
   </si>
   <si>
     <t>These units exist in EPA without a generator ID. They are likely industrial units and not in the EIA database, but we welcome research or information on these units</t>
+  </si>
+  <si>
+    <t>Generator is missing from EPA, but shows up in EIA-860 2018 retired sheet</t>
+  </si>
+  <si>
+    <t>Unit retired in 2010 according to EIA-860 2010. See EIA-860 2010. No reported emissions in EPA</t>
+  </si>
+  <si>
+    <t>Unit began operating in 2019 (even though it shows up in EPA's database in 2018).</t>
+  </si>
+  <si>
+    <t>Unit retired in 2007, still listed as operating in EPA database. Match verified using the Retired tab of the EIA-860.</t>
+  </si>
+  <si>
+    <t>BLR01A</t>
+  </si>
+  <si>
+    <t>BLR01B</t>
+  </si>
+  <si>
+    <t>BLR01C</t>
+  </si>
+  <si>
+    <t>BLR02A</t>
+  </si>
+  <si>
+    <t>BLR02B</t>
+  </si>
+  <si>
+    <t>BLR02C</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Only 2018</t>
+  </si>
+  <si>
+    <t>Not grid connected.</t>
+  </si>
+  <si>
+    <t>H8</t>
+  </si>
+  <si>
+    <t>H9</t>
+  </si>
+  <si>
+    <t>Retired</t>
+  </si>
+  <si>
+    <t>Retired in 2019</t>
+  </si>
+  <si>
+    <t>**2A</t>
+  </si>
+  <si>
+    <t>**2B</t>
+  </si>
+  <si>
+    <t>1SG</t>
+  </si>
+  <si>
+    <t>002001</t>
+  </si>
+  <si>
+    <t>EUBHB9</t>
+  </si>
+  <si>
+    <t>BLR08</t>
+  </si>
+  <si>
+    <t>PR003</t>
+  </si>
+  <si>
+    <t>PR004</t>
+  </si>
+  <si>
+    <t>PR005</t>
+  </si>
+  <si>
+    <t>AAB01</t>
+  </si>
+  <si>
+    <t>150137</t>
+  </si>
+  <si>
+    <t>150138</t>
+  </si>
+  <si>
+    <t>150139</t>
+  </si>
+  <si>
+    <t>150140</t>
+  </si>
+  <si>
+    <t>150145</t>
+  </si>
+  <si>
+    <t>CT1</t>
+  </si>
+  <si>
+    <t>DES1</t>
+  </si>
+  <si>
+    <t>DES2</t>
+  </si>
+  <si>
+    <t>CTP</t>
+  </si>
+  <si>
+    <t>214JA</t>
+  </si>
+  <si>
+    <t>214JB</t>
+  </si>
+  <si>
+    <t>B921A</t>
+  </si>
+  <si>
+    <t>5STA</t>
+  </si>
+  <si>
+    <t>5STB</t>
+  </si>
+  <si>
+    <t>B921B</t>
+  </si>
+  <si>
+    <t>GT501A</t>
+  </si>
+  <si>
+    <t>GT501B</t>
+  </si>
+  <si>
+    <t>5B921A</t>
+  </si>
+  <si>
+    <t>5B921B</t>
+  </si>
+  <si>
+    <t>5L501A</t>
+  </si>
+  <si>
+    <t>5L501B</t>
+  </si>
+  <si>
+    <t>Retired in 2019 and not in EIA data at all</t>
+  </si>
+  <si>
+    <t>Not operating since 2019</t>
+  </si>
+  <si>
+    <t>In Long Term Cold Storage (LTCS), not in 860 or 923</t>
+  </si>
+  <si>
+    <t>Closed in 2020 not in 860 or 923</t>
+  </si>
+  <si>
+    <t>Retired and not in 860 or 923</t>
+  </si>
+  <si>
+    <t>Not operating in 2021</t>
+  </si>
+  <si>
+    <t>Partially retired in 2019 and partially not connected to the grid. Not in EIA at all</t>
+  </si>
+  <si>
+    <t>LTCS in 2019 and not in EIA data at all</t>
+  </si>
+  <si>
+    <t>In Long Term Cold Storage, not in 860 or 923</t>
+  </si>
+  <si>
+    <t>Cabrillo Power I Encina Power Station</t>
+  </si>
+  <si>
+    <t>AES Alamitos</t>
+  </si>
+  <si>
+    <t>Carlsbad Energy Center</t>
+  </si>
+  <si>
+    <t>AES Alamitos Energy Center</t>
+  </si>
+  <si>
+    <t>AES Huntington Beach</t>
+  </si>
+  <si>
+    <t>AES Huntington Beach Energy Project</t>
+  </si>
+  <si>
+    <t>Lauderdale</t>
+  </si>
+  <si>
+    <t>Dania Beach 7</t>
+  </si>
+  <si>
+    <t>Wayne County</t>
+  </si>
+  <si>
+    <t>V H Braunig</t>
+  </si>
+  <si>
+    <t>Arthur Von Rosenberg</t>
+  </si>
+  <si>
+    <t>AG1</t>
+  </si>
+  <si>
+    <t>AG2</t>
+  </si>
+  <si>
+    <t>COS3</t>
+  </si>
+  <si>
+    <t>COS4</t>
+  </si>
+  <si>
+    <t>COS5</t>
+  </si>
+  <si>
+    <t>COS6</t>
+  </si>
+  <si>
+    <t>SJ10</t>
+  </si>
+  <si>
+    <t>SJ7</t>
+  </si>
+  <si>
+    <t>SJ8</t>
+  </si>
+  <si>
+    <t>SJ9</t>
+  </si>
+  <si>
+    <t>PS1</t>
+  </si>
+  <si>
+    <t>PS2</t>
+  </si>
+  <si>
+    <t>PS3</t>
+  </si>
+  <si>
+    <t>PS4</t>
+  </si>
+  <si>
+    <t>UNIT1</t>
+  </si>
+  <si>
+    <t>UNIT2</t>
   </si>
 </sst>
 </file>
@@ -2195,7 +2438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -2209,13 +2452,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
@@ -2250,7 +2493,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2273,7 +2516,7 @@
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2296,7 +2539,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2319,7 +2562,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2342,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2365,7 +2608,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2388,7 +2631,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2411,7 +2654,7 @@
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2434,7 +2677,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2631,7 +2874,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D20" s="6">
         <v>7903</v>
@@ -2640,7 +2883,7 @@
         <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2651,7 +2894,7 @@
         <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D21" s="6">
         <v>7903</v>
@@ -2660,7 +2903,7 @@
         <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3365,7 +3608,7 @@
         <v>106</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3396,7 +3639,7 @@
         <v>40</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D56" s="6">
         <v>50561</v>
@@ -3405,10 +3648,10 @@
         <v>40</v>
       </c>
       <c r="F56" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3416,22 +3659,22 @@
         <v>50561</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D57" s="6">
         <v>50561</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F57" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3439,19 +3682,19 @@
         <v>55464</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D58" s="6">
         <v>55464</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3459,22 +3702,22 @@
         <v>55708</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D59" s="6">
         <v>55708</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3482,19 +3725,19 @@
         <v>56963</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D60" s="6">
         <v>56963</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3502,19 +3745,19 @@
         <v>56963</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D61" s="6">
         <v>56963</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3525,7 +3768,7 @@
         <v>15</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D62" s="6">
         <v>57842</v>
@@ -3534,7 +3777,7 @@
         <v>6</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3542,10 +3785,10 @@
         <v>58503</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D63" s="6">
         <v>58503</v>
@@ -3554,7 +3797,7 @@
         <v>69</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3562,7 +3805,7 @@
         <v>58503</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>11</v>
@@ -3574,7 +3817,7 @@
         <v>71</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3582,19 +3825,19 @@
         <v>63628</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D65" s="6">
         <v>2953</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3602,19 +3845,19 @@
         <v>63628</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D66" s="6">
         <v>2953</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3622,19 +3865,19 @@
         <v>63628</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D67" s="6">
         <v>2953</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3642,19 +3885,19 @@
         <v>63628</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D68" s="6">
         <v>2953</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3662,19 +3905,19 @@
         <v>7909</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="G69" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3682,19 +3925,19 @@
         <v>7909</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="G70" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3705,16 +3948,16 @@
         <v>34</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3725,16 +3968,16 @@
         <v>62</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3751,10 +3994,10 @@
         <v>56480</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3771,10 +4014,234 @@
         <v>56480</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>880102</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="6">
+        <v>61082</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>880102</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2</v>
+      </c>
+      <c r="D76" s="6">
+        <v>61082</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>880105</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D77" s="6">
+        <v>61146</v>
+      </c>
+      <c r="F77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>880105</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D78" s="6">
+        <v>61146</v>
+      </c>
+      <c r="F78" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>880104</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D79" s="6">
+        <v>61147</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>880104</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D80" s="6">
+        <v>61147</v>
+      </c>
+      <c r="E80" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>880104</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D81" s="6">
+        <v>61147</v>
+      </c>
+      <c r="E81" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>880104</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D82" s="6">
+        <v>61147</v>
+      </c>
+      <c r="E82" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>880106</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D83" s="6">
+        <v>61148</v>
+      </c>
+      <c r="E83" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>880106</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D84" s="6">
+        <v>61148</v>
+      </c>
+      <c r="E84" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>880107</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D85" s="6">
+        <v>61148</v>
+      </c>
+      <c r="E85" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>880108</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D86" s="6">
+        <v>61148</v>
+      </c>
+      <c r="E86" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>880103</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D87" s="6">
+        <v>61149</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>880103</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D88" s="6">
+        <v>61149</v>
+      </c>
+      <c r="E88" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>880103</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D89" s="6">
+        <v>61149</v>
+      </c>
+      <c r="E89" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>880103</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D90" s="6">
+        <v>61149</v>
+      </c>
+      <c r="E90" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3787,2255 +4254,4668 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>409</v>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>404</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D1" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="6">
+        <v>127</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2">
+        <v>127</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2012</v>
+      </c>
+      <c r="B3" s="6">
+        <v>228</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="1">
+        <v>228</v>
+      </c>
+      <c r="F3" s="1">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4" s="6">
+        <v>228</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="1">
+        <v>228</v>
+      </c>
+      <c r="F4" s="1">
+        <v>9</v>
+      </c>
+      <c r="G4" s="1">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2012</v>
+      </c>
+      <c r="B5" s="6">
+        <v>259</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3">
+        <v>259</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2012</v>
+      </c>
+      <c r="B6" s="6">
+        <v>259</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3">
+        <v>259</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2012</v>
+      </c>
+      <c r="B7" s="6">
+        <v>259</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>259</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2012</v>
+      </c>
+      <c r="B8" s="6">
+        <v>259</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>259</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2012</v>
+      </c>
+      <c r="B9" s="6">
+        <v>271</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3">
+        <v>271</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2012</v>
+      </c>
+      <c r="B10" s="6">
+        <v>271</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="3">
+        <v>271</v>
+      </c>
+      <c r="F10" s="1">
+        <v>6</v>
+      </c>
+      <c r="G10" s="1">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2012</v>
+      </c>
+      <c r="B11" s="6">
+        <v>271</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="3">
+        <v>271</v>
+      </c>
+      <c r="F11" s="1">
+        <v>7</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7</v>
+      </c>
+      <c r="H11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2010</v>
+      </c>
+      <c r="B12" s="6">
+        <v>273</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>273</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2010</v>
+      </c>
+      <c r="B13" s="2">
+        <v>310</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="2">
+        <v>310</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2010</v>
+      </c>
+      <c r="B14" s="2">
+        <v>310</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2">
+        <v>310</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2010</v>
+      </c>
+      <c r="B15" s="2">
+        <v>356</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2018</v>
+      </c>
+      <c r="B16" s="2">
+        <v>389</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2">
+        <v>389</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="6">
+        <v>478</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1">
+        <v>478</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2016</v>
+      </c>
+      <c r="B18" s="6">
+        <v>478</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1">
+        <v>478</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2016</v>
+      </c>
+      <c r="B19" s="6">
+        <v>478</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1">
+        <v>478</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2021</v>
+      </c>
+      <c r="B20" s="6">
+        <v>764</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E20" s="6">
+        <v>764</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2021</v>
+      </c>
+      <c r="B21" s="6">
+        <v>764</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E21" s="6">
+        <v>764</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1552</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1552</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2020</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1552</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1552</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2016</v>
+      </c>
+      <c r="B24" s="7">
         <v>1594</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="G2" t="s">
+      <c r="E24" s="3"/>
+      <c r="G24" s="4"/>
+      <c r="H24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2016</v>
+      </c>
+      <c r="B25" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="G25" s="4"/>
+      <c r="H25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2016</v>
+      </c>
+      <c r="B26" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2016</v>
+      </c>
+      <c r="B27" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2016</v>
+      </c>
+      <c r="B28" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2016</v>
+      </c>
+      <c r="B29" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2016</v>
+      </c>
+      <c r="B30" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2016</v>
+      </c>
+      <c r="B31" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2016</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2440</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="H32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2005</v>
+      </c>
+      <c r="B33" s="7">
+        <v>2504</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2005</v>
+      </c>
+      <c r="B34" s="7">
+        <v>2504</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2005</v>
+      </c>
+      <c r="B35" s="7">
+        <v>2504</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2020</v>
+      </c>
+      <c r="B36" s="6">
+        <v>2535</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2535</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2020</v>
+      </c>
+      <c r="B37" s="6">
+        <v>2535</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2535</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2018</v>
+      </c>
+      <c r="B38" s="7">
+        <v>2549</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2018</v>
+      </c>
+      <c r="B39" s="7">
+        <v>2549</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2021</v>
+      </c>
+      <c r="B40" s="6">
+        <v>2837</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="6">
+        <v>2837</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2020</v>
+      </c>
+      <c r="B41" s="6">
+        <v>3344</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3344</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2020</v>
+      </c>
+      <c r="B42" s="6">
+        <v>3344</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3344</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2022</v>
+      </c>
+      <c r="B43" s="6">
+        <v>3946</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="6">
+        <v>3946</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2022</v>
+      </c>
+      <c r="B44" s="6">
+        <v>3946</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="6">
+        <v>3946</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2021</v>
+      </c>
+      <c r="B45" s="6">
+        <v>6082</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="6">
+        <v>6082</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2021</v>
+      </c>
+      <c r="B46" s="6">
+        <v>6094</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="1">
+        <v>6094</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2021</v>
+      </c>
+      <c r="B47" s="6">
+        <v>6094</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="1">
+        <v>6094</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2021</v>
+      </c>
+      <c r="B48" s="6">
+        <v>6094</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="G3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="1">
+        <v>6094</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2021</v>
+      </c>
+      <c r="B49" s="6">
+        <v>6106</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="E49" s="1">
+        <v>6106</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>2549</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>2549</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="H49" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2020</v>
+      </c>
+      <c r="B50" s="6">
+        <v>6136</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="6">
+        <v>6136</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2023</v>
+      </c>
+      <c r="B51" s="6">
+        <v>6776</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="6">
+        <v>6776</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2018</v>
+      </c>
+      <c r="B52" s="2">
+        <v>10071</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2018</v>
+      </c>
+      <c r="B53" s="2">
+        <v>10071</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2018</v>
+      </c>
+      <c r="B54" s="2">
+        <v>10071</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H54" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2018</v>
+      </c>
+      <c r="B55" s="2">
+        <v>10071</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H55" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2018</v>
+      </c>
+      <c r="B56" s="2">
+        <v>10071</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2018</v>
+      </c>
+      <c r="B57" s="2">
+        <v>10071</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2016</v>
+      </c>
+      <c r="B58" s="6">
+        <v>10111</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2021</v>
+      </c>
+      <c r="B59" s="6">
+        <v>10350</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="6">
+        <v>10350</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H59" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2021</v>
+      </c>
+      <c r="B60" s="6">
+        <v>10350</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="6">
+        <v>10350</v>
+      </c>
+      <c r="F60"/>
+      <c r="G60" t="s">
+        <v>71</v>
+      </c>
+      <c r="H60" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2016</v>
+      </c>
+      <c r="B61" s="6">
+        <v>10381</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H61" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2016</v>
+      </c>
+      <c r="B62" s="6">
+        <v>10381</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2020</v>
+      </c>
+      <c r="B63" s="6">
+        <v>10384</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="1">
+        <v>10384</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H63" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2020</v>
+      </c>
+      <c r="B64" s="6">
+        <v>10384</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="1">
+        <v>10384</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H64" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2020</v>
+      </c>
+      <c r="B65" s="6">
+        <v>10384</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E65" s="1">
+        <v>10384</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H65" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2020</v>
+      </c>
+      <c r="B66" s="6">
+        <v>10384</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" s="1">
+        <v>10384</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H66" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2016</v>
+      </c>
+      <c r="B67" s="8">
+        <v>10675</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="D67" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2016</v>
+      </c>
+      <c r="B68" s="8">
         <v>10675</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <v>10675</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="E68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2023</v>
+      </c>
+      <c r="B69" s="6">
+        <v>10698</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="E69" s="6">
+        <v>10698</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2016</v>
+      </c>
+      <c r="B70" s="2">
+        <v>10788</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D70" s="2"/>
+      <c r="H70" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2007</v>
+      </c>
+      <c r="B71" s="6">
+        <v>10803</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="D71" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="6">
+        <v>10803</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2007</v>
+      </c>
+      <c r="B72" s="6">
+        <v>10803</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G22" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>880004</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>880006</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="D72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72" s="6">
+        <v>10803</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2016</v>
+      </c>
+      <c r="B73" s="2">
+        <v>50044</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D73" s="2"/>
+      <c r="H73" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2021</v>
+      </c>
+      <c r="B74">
+        <v>50137</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
-        <v>880006</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="D74" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74">
+        <v>50137</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2016</v>
+      </c>
+      <c r="B75" s="2">
+        <v>50151</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H75" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2016</v>
+      </c>
+      <c r="B76" s="2">
+        <v>50151</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H76" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2018</v>
+      </c>
+      <c r="B77" s="2">
+        <v>50202</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H77" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2016</v>
+      </c>
+      <c r="B78">
+        <v>50247</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H78" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2016</v>
+      </c>
+      <c r="B79">
+        <v>50247</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H79" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2016</v>
+      </c>
+      <c r="B80">
+        <v>50247</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>880006</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>880006</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>880007</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>880016</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>880016</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>880016</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G31" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>880023</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G32" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>880023</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G33" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>880023</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>880023</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>880024</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G36" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>880025</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>880025</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>880025</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
-        <v>880025</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G40" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>880028</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G41" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>880029</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>880030</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G43" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>880030</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G44" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>880031</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G45" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
-        <v>880031</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G46" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>880033</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G47" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>880038</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>880039</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G49" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
-        <v>880039</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G50" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>880041</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G51" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
-        <v>880041</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G52" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
-        <v>880041</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G53" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
-        <v>880042</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G54" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
-        <v>880042</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G55" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>880042</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G56" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>880042</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G57" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>880043</v>
-      </c>
-      <c r="B58" s="1" t="s">
+      <c r="H80" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2016</v>
+      </c>
+      <c r="B81">
+        <v>50247</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G58" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>880044</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G59" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>880045</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G60" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>880045</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G61" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
-        <v>880045</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G62" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
-        <v>880049</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G63" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
-        <v>880050</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G64" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
-        <v>880052</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G65" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
-        <v>880053</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G66" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
-        <v>880053</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G67" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
-        <v>880053</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G68" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
-        <v>880053</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G69" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
-        <v>880053</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G70" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
-        <v>880055</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G71" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
-        <v>880055</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
-        <v>880055</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G73" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
-        <v>880057</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G74" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>880057</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="H81" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2020</v>
+      </c>
+      <c r="B82">
+        <v>50282</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82">
+        <v>50282</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H82" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2020</v>
+      </c>
+      <c r="B83">
+        <v>50282</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E83">
+        <v>50282</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H83" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2020</v>
+      </c>
+      <c r="B84">
+        <v>50282</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84">
+        <v>50282</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H84" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2020</v>
+      </c>
+      <c r="B85">
+        <v>50282</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E85">
+        <v>50282</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H85" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2020</v>
+      </c>
+      <c r="B86">
+        <v>50282</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86">
+        <v>50282</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H86" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2020</v>
+      </c>
+      <c r="B87">
+        <v>50282</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E87">
+        <v>50282</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H87" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2016</v>
+      </c>
+      <c r="B88" s="2">
+        <v>50607</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D88" s="2"/>
+      <c r="H88" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2016</v>
+      </c>
+      <c r="B89" s="2">
+        <v>50607</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="H89" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>2016</v>
+      </c>
+      <c r="B90" s="2">
+        <v>50607</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D90" s="2"/>
+      <c r="H90" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2016</v>
+      </c>
+      <c r="B91" s="2">
+        <v>50607</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D91" s="2"/>
+      <c r="H91" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>2016</v>
+      </c>
+      <c r="B92" s="2">
+        <v>50607</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D92" s="2"/>
+      <c r="H92" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>2023</v>
+      </c>
+      <c r="B93">
+        <v>50852</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93">
+        <v>50852</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>2023</v>
+      </c>
+      <c r="B94">
+        <v>50852</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E94">
+        <v>50852</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>2021</v>
+      </c>
+      <c r="B95">
+        <v>50976</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G75" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
-        <v>880065</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G76" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
-        <v>880065</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
-        <v>880067</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
-        <v>880067</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G79" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
-        <v>880067</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G80" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
-        <v>880067</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G81" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
-        <v>880071</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G82" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
-        <v>880072</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G83" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
-        <v>880074</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G84" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
-        <v>880075</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G85" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
-        <v>880075</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G86" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
-        <v>880076</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G87" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
-        <v>880076</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G88" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
-        <v>880076</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G89" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
-        <v>880078</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G90" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
-        <v>880079</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G91" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
-        <v>880079</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G92" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
-        <v>880079</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G93" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
-        <v>880079</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G94" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
-        <v>880083</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G95" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
-        <v>880086</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G96" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
-        <v>880086</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G97" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
-        <v>880086</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G98" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
-        <v>880087</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G99" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
-        <v>880088</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G100" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
-        <v>880088</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G101" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
-        <v>880088</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G102" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
-        <v>880089</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G103" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
-        <v>880092</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G104" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
-        <v>880092</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G105" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
-        <v>880093</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G106" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
-        <v>880093</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G107" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
-        <v>880096</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G108" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
-        <v>880100</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G109" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
-        <v>880100</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G110" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
-        <v>880100</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G111" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
-        <v>880100</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G112" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
-        <v>880101</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G113" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
-        <v>880102</v>
-      </c>
-      <c r="B114" s="1" t="s">
+      <c r="D95" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95">
+        <v>50976</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>2010</v>
+      </c>
+      <c r="B96" s="2">
+        <v>51000</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>2020</v>
+      </c>
+      <c r="B97">
+        <v>52106</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H97" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>2020</v>
+      </c>
+      <c r="B98">
+        <v>52106</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="H98" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>2020</v>
+      </c>
+      <c r="B99">
+        <v>52106</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H99" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>2020</v>
+      </c>
+      <c r="B100">
+        <v>52106</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H100" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>2020</v>
+      </c>
+      <c r="B101">
+        <v>52106</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H101" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2018</v>
+      </c>
+      <c r="B102" s="2">
+        <v>54035</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="D102" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H102" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2016</v>
+      </c>
+      <c r="B103" s="6">
+        <v>54571</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="6">
+        <v>54571</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>2016</v>
+      </c>
+      <c r="B104" s="6">
+        <v>54571</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E104" s="6">
+        <v>54571</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>2016</v>
+      </c>
+      <c r="B105" s="6">
+        <v>54571</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E105" s="6">
+        <v>54571</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>2016</v>
+      </c>
+      <c r="B106" s="6">
+        <v>54571</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E106" s="6">
+        <v>54571</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>2016</v>
+      </c>
+      <c r="B107" s="2">
+        <v>54571</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H107" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>2016</v>
+      </c>
+      <c r="B108" s="2">
+        <v>54571</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H108" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>2016</v>
+      </c>
+      <c r="B109" s="2">
+        <v>54571</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H109" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>2016</v>
+      </c>
+      <c r="B110" s="2">
+        <v>54571</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H110" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>2018</v>
+      </c>
+      <c r="B111" s="2">
+        <v>54755</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H111" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>2018</v>
+      </c>
+      <c r="B112" s="6">
+        <v>55098</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>2018</v>
+      </c>
+      <c r="B113" s="6">
+        <v>55098</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>2018</v>
+      </c>
+      <c r="B114" s="6">
+        <v>55098</v>
+      </c>
       <c r="C114" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G114" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
-        <v>880102</v>
-      </c>
-      <c r="B115" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>2018</v>
+      </c>
+      <c r="B115" s="6">
+        <v>55098</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
-        <v>880107</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G116" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
-        <v>880107</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G117" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
-        <v>880107</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G118" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
-        <v>880107</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G119" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
-        <v>880108</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G120" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
-        <v>880108</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G121" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
-        <v>228</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>18</v>
+      <c r="D115" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>2018</v>
+      </c>
+      <c r="B116" s="2">
+        <v>55098</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H116" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>2018</v>
+      </c>
+      <c r="B117" s="2">
+        <v>55098</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H117" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>2018</v>
+      </c>
+      <c r="B118" s="2">
+        <v>55098</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H118" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>2018</v>
+      </c>
+      <c r="B119" s="2">
+        <v>55098</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H119" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>2016</v>
+      </c>
+      <c r="B120">
+        <v>55422</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="H120" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>2016</v>
+      </c>
+      <c r="B121">
+        <v>55422</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H121" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>424</v>
+      </c>
+      <c r="B122" s="6">
+        <v>55524</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D122" s="1">
-        <v>228</v>
-      </c>
-      <c r="E122" s="1">
-        <v>10</v>
-      </c>
-      <c r="F122" s="1">
+        <v>30</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>424</v>
+      </c>
+      <c r="B123" s="6">
+        <v>55524</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>424</v>
+      </c>
+      <c r="B124" s="6">
+        <v>55524</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>424</v>
+      </c>
+      <c r="B125" s="6">
+        <v>55524</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>2018</v>
+      </c>
+      <c r="B126" s="6">
+        <v>55699</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H126" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>2016</v>
+      </c>
+      <c r="B127" s="2">
+        <v>55703</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D127" s="2"/>
+      <c r="H127" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>2020</v>
+      </c>
+      <c r="B128">
+        <v>55833</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H128" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>2021</v>
+      </c>
+      <c r="B129">
+        <v>59073</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E129" s="1">
+        <v>59073</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>2021</v>
+      </c>
+      <c r="B130">
+        <v>59073</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E130" s="1">
+        <v>59073</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>2021</v>
+      </c>
+      <c r="B131">
+        <v>59073</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E131" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>2021</v>
+      </c>
+      <c r="B132">
+        <v>59073</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E132" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>2021</v>
+      </c>
+      <c r="B133">
+        <v>59073</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E133" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>2021</v>
+      </c>
+      <c r="B134">
+        <v>59073</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E134" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>2021</v>
+      </c>
+      <c r="B135">
+        <v>59073</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E135" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>2021</v>
+      </c>
+      <c r="B136">
+        <v>59073</v>
+      </c>
+      <c r="C136" t="s">
+        <v>455</v>
+      </c>
+      <c r="D136" t="s">
+        <v>453</v>
+      </c>
+      <c r="E136">
+        <v>59073</v>
+      </c>
+      <c r="F136" t="s">
+        <v>459</v>
+      </c>
+      <c r="G136" t="s">
+        <v>453</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>2021</v>
+      </c>
+      <c r="B137">
+        <v>59073</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E137" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>2021</v>
+      </c>
+      <c r="B138">
+        <v>59073</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E138" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>2018</v>
+      </c>
+      <c r="B139" s="6">
+        <v>60345</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E139" s="6">
+        <v>60345</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>2018</v>
+      </c>
+      <c r="B140" s="6">
+        <v>60345</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E140" s="6">
+        <v>60345</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>2018</v>
+      </c>
+      <c r="B141" s="6">
+        <v>60345</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G122" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
-        <v>228</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C123" s="1" t="s">
+      <c r="E141" s="6">
+        <v>60345</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>2018</v>
+      </c>
+      <c r="B142" s="6">
+        <v>60345</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E142" s="6">
+        <v>60345</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>2018</v>
+      </c>
+      <c r="B143" s="6">
+        <v>60345</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E143" s="6">
+        <v>60345</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>2018</v>
+      </c>
+      <c r="B144" s="6">
+        <v>60345</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E144" s="6">
+        <v>60345</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>423</v>
+      </c>
+      <c r="B145" s="6">
+        <v>880004</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>423</v>
+      </c>
+      <c r="B146" s="6">
+        <v>880004</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H146" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>423</v>
+      </c>
+      <c r="B147" s="6">
+        <v>880004</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H147" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>423</v>
+      </c>
+      <c r="B148" s="6">
+        <v>880004</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H148" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>423</v>
+      </c>
+      <c r="B149" s="6">
+        <v>880004</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H149" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>423</v>
+      </c>
+      <c r="B150" s="6">
+        <v>880004</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H150" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>423</v>
+      </c>
+      <c r="B151" s="6">
+        <v>880004</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D123" s="1">
-        <v>228</v>
-      </c>
-      <c r="E123" s="1">
-        <v>9</v>
-      </c>
-      <c r="F123" s="1">
-        <v>6</v>
-      </c>
-      <c r="G123" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
-        <v>259</v>
-      </c>
-      <c r="B124" s="1" t="s">
+      <c r="H151" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>423</v>
+      </c>
+      <c r="B152" s="6">
+        <v>880006</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D124" s="3">
-        <v>259</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G124" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
-        <v>259</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D125" s="3">
-        <v>259</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G125" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
-        <v>259</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D126" s="3">
-        <v>259</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G126" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
-        <v>259</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D127" s="3">
-        <v>259</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G127" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
-        <v>271</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D128" s="3">
-        <v>271</v>
-      </c>
-      <c r="E128" s="1">
-        <v>5</v>
-      </c>
-      <c r="F128" s="1">
-        <v>5</v>
-      </c>
-      <c r="G128" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
-        <v>271</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D129" s="3">
-        <v>271</v>
-      </c>
-      <c r="E129" s="1">
-        <v>6</v>
-      </c>
-      <c r="F129" s="1">
-        <v>6</v>
-      </c>
-      <c r="G129" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
-        <v>271</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D130" s="3">
-        <v>271</v>
-      </c>
-      <c r="E130" s="1">
-        <v>7</v>
-      </c>
-      <c r="F130" s="1">
-        <v>7</v>
-      </c>
-      <c r="G130" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
-        <v>273</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D131" s="3">
-        <v>273</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F131" s="1">
-        <v>3</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
-        <v>310</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D132" s="2">
-        <v>310</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
-        <v>310</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D133" s="2">
-        <v>310</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
-        <v>356</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
-        <v>389</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D135" s="2">
-        <v>389</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>51000</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
-        <v>54571</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D141" s="6">
-        <v>54571</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
-        <v>54571</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D142" s="6">
-        <v>54571</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
-        <v>54571</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D143" s="6">
-        <v>54571</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
-        <v>54571</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D144" s="6">
-        <v>54571</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
-        <v>55098</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
-        <v>55098</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
-        <v>55098</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
-        <v>55098</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
-        <v>55524</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
-        <v>55524</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
-        <v>55524</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
-        <v>55524</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
-        <v>55699</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>17</v>
+      <c r="H152" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>423</v>
+      </c>
+      <c r="B153" s="6">
+        <v>880006</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G153" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="6">
-        <v>60345</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>383</v>
+      <c r="H153" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>423</v>
+      </c>
+      <c r="B154" s="6">
+        <v>880006</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D154" s="6">
-        <v>60345</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
-        <v>60345</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>383</v>
+        <v>25</v>
+      </c>
+      <c r="H154" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>423</v>
+      </c>
+      <c r="B155" s="6">
+        <v>880006</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D155" s="6">
-        <v>60345</v>
-      </c>
-      <c r="E155" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H155" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>423</v>
+      </c>
+      <c r="B156" s="6">
+        <v>880007</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H156" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>423</v>
+      </c>
+      <c r="B157" s="6">
+        <v>880016</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H157" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>423</v>
+      </c>
+      <c r="B158" s="6">
+        <v>880016</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H158" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>423</v>
+      </c>
+      <c r="B159" s="6">
+        <v>880016</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H159" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>423</v>
+      </c>
+      <c r="B160" s="6">
+        <v>880023</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H160" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>423</v>
+      </c>
+      <c r="B161" s="6">
+        <v>880023</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H161" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>423</v>
+      </c>
+      <c r="B162" s="6">
+        <v>880023</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H162" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>423</v>
+      </c>
+      <c r="B163" s="6">
+        <v>880023</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H163" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>423</v>
+      </c>
+      <c r="B164" s="6">
+        <v>880024</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H164" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>423</v>
+      </c>
+      <c r="B165" s="6">
+        <v>880025</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H165" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>423</v>
+      </c>
+      <c r="B166" s="6">
+        <v>880025</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H166" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>423</v>
+      </c>
+      <c r="B167" s="6">
+        <v>880025</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H167" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>423</v>
+      </c>
+      <c r="B168" s="6">
+        <v>880025</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H168" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>423</v>
+      </c>
+      <c r="B169" s="6">
+        <v>880028</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H169" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>423</v>
+      </c>
+      <c r="B170" s="6">
+        <v>880029</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H170" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>423</v>
+      </c>
+      <c r="B171" s="6">
+        <v>880030</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H171" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>423</v>
+      </c>
+      <c r="B172" s="6">
+        <v>880030</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H172" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>423</v>
+      </c>
+      <c r="B173" s="6">
+        <v>880031</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H173" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>423</v>
+      </c>
+      <c r="B174" s="6">
+        <v>880031</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H174" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>423</v>
+      </c>
+      <c r="B175" s="6">
+        <v>880033</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H175" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>423</v>
+      </c>
+      <c r="B176" s="6">
+        <v>880038</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H176" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>423</v>
+      </c>
+      <c r="B177" s="6">
+        <v>880039</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H177" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>423</v>
+      </c>
+      <c r="B178" s="6">
+        <v>880039</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H178" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>423</v>
+      </c>
+      <c r="B179" s="6">
+        <v>880041</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H179" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>423</v>
+      </c>
+      <c r="B180" s="6">
+        <v>880041</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H180" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>423</v>
+      </c>
+      <c r="B181" s="6">
+        <v>880041</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H181" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>423</v>
+      </c>
+      <c r="B182" s="6">
+        <v>880042</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H182" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>423</v>
+      </c>
+      <c r="B183" s="6">
+        <v>880042</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H183" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>423</v>
+      </c>
+      <c r="B184" s="6">
+        <v>880042</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H184" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>423</v>
+      </c>
+      <c r="B185" s="6">
+        <v>880042</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H185" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>423</v>
+      </c>
+      <c r="B186" s="6">
+        <v>880043</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F155" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
-        <v>60345</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D156" s="6">
-        <v>60345</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
-        <v>60345</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D157" s="6">
-        <v>60345</v>
-      </c>
-      <c r="E157" s="1" t="s">
+      <c r="H186" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>423</v>
+      </c>
+      <c r="B187" s="6">
+        <v>880044</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H187" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>423</v>
+      </c>
+      <c r="B188" s="6">
+        <v>880045</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H188" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>423</v>
+      </c>
+      <c r="B189" s="6">
+        <v>880045</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H189" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>423</v>
+      </c>
+      <c r="B190" s="6">
+        <v>880045</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H190" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>423</v>
+      </c>
+      <c r="B191" s="6">
+        <v>880049</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H191" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>423</v>
+      </c>
+      <c r="B192" s="6">
+        <v>880050</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H192" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>423</v>
+      </c>
+      <c r="B193" s="6">
+        <v>880052</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H193" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>423</v>
+      </c>
+      <c r="B194" s="6">
+        <v>880053</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H194" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>423</v>
+      </c>
+      <c r="B195" s="6">
+        <v>880053</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H195" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>423</v>
+      </c>
+      <c r="B196" s="6">
+        <v>880053</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H196" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>423</v>
+      </c>
+      <c r="B197" s="6">
+        <v>880053</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H197" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>423</v>
+      </c>
+      <c r="B198" s="6">
+        <v>880053</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H198" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>423</v>
+      </c>
+      <c r="B199" s="6">
+        <v>880055</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H199" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>423</v>
+      </c>
+      <c r="B200" s="6">
+        <v>880055</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H200" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>423</v>
+      </c>
+      <c r="B201" s="6">
+        <v>880055</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H201" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>423</v>
+      </c>
+      <c r="B202" s="6">
+        <v>880057</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H202" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>423</v>
+      </c>
+      <c r="B203" s="6">
+        <v>880057</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H203" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>423</v>
+      </c>
+      <c r="B204" s="6">
+        <v>880065</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H204" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>423</v>
+      </c>
+      <c r="B205" s="6">
+        <v>880065</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H205" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>423</v>
+      </c>
+      <c r="B206" s="6">
+        <v>880067</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H206" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>423</v>
+      </c>
+      <c r="B207" s="6">
+        <v>880067</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H207" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>423</v>
+      </c>
+      <c r="B208" s="6">
+        <v>880067</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H208" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>423</v>
+      </c>
+      <c r="B209" s="6">
+        <v>880067</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H209" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>423</v>
+      </c>
+      <c r="B210" s="6">
+        <v>880071</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H210" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>423</v>
+      </c>
+      <c r="B211" s="6">
+        <v>880072</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H211" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>423</v>
+      </c>
+      <c r="B212" s="6">
+        <v>880074</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H212" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>423</v>
+      </c>
+      <c r="B213" s="6">
+        <v>880075</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H213" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>423</v>
+      </c>
+      <c r="B214" s="6">
+        <v>880075</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H214" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>423</v>
+      </c>
+      <c r="B215" s="6">
+        <v>880076</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H215" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>423</v>
+      </c>
+      <c r="B216" s="6">
+        <v>880076</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H216" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>423</v>
+      </c>
+      <c r="B217" s="6">
+        <v>880076</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H217" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>423</v>
+      </c>
+      <c r="B218" s="6">
+        <v>880078</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H218" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>423</v>
+      </c>
+      <c r="B219" s="6">
+        <v>880079</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H219" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>423</v>
+      </c>
+      <c r="B220" s="6">
+        <v>880079</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H220" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>423</v>
+      </c>
+      <c r="B221" s="6">
+        <v>880079</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H221" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>423</v>
+      </c>
+      <c r="B222" s="6">
+        <v>880079</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H222" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>423</v>
+      </c>
+      <c r="B223" s="6">
+        <v>880083</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H223" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>423</v>
+      </c>
+      <c r="B224" s="6">
+        <v>880086</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H224" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>423</v>
+      </c>
+      <c r="B225" s="6">
+        <v>880086</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H225" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>423</v>
+      </c>
+      <c r="B226" s="6">
+        <v>880086</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H226" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>423</v>
+      </c>
+      <c r="B227" s="6">
+        <v>880087</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H227" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>423</v>
+      </c>
+      <c r="B228" s="6">
+        <v>880088</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H228" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>423</v>
+      </c>
+      <c r="B229" s="6">
+        <v>880088</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H229" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>423</v>
+      </c>
+      <c r="B230" s="6">
+        <v>880088</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H230" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>423</v>
+      </c>
+      <c r="B231" s="6">
+        <v>880089</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H231" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>423</v>
+      </c>
+      <c r="B232" s="6">
+        <v>880092</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H232" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>423</v>
+      </c>
+      <c r="B233" s="6">
+        <v>880092</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H233" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>423</v>
+      </c>
+      <c r="B234" s="6">
+        <v>880093</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H234" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>423</v>
+      </c>
+      <c r="B235" s="6">
+        <v>880093</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H235" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>423</v>
+      </c>
+      <c r="B236" s="6">
+        <v>880096</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H236" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>423</v>
+      </c>
+      <c r="B237" s="6">
+        <v>880100</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H237" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>423</v>
+      </c>
+      <c r="B238" s="6">
+        <v>880100</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H238" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>423</v>
+      </c>
+      <c r="B239" s="6">
+        <v>880100</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H239" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>423</v>
+      </c>
+      <c r="B240" s="6">
+        <v>880100</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H240" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>423</v>
+      </c>
+      <c r="B241" s="6">
+        <v>880101</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H241" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>423</v>
+      </c>
+      <c r="B242" s="6">
+        <v>880102</v>
+      </c>
+      <c r="C242" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F157" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
-        <v>60345</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D158" s="6">
-        <v>60345</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
-        <v>60345</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D159" s="6">
-        <v>60345</v>
-      </c>
-      <c r="E159" s="1" t="s">
+      <c r="D242" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F159" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
-        <v>10803</v>
-      </c>
-      <c r="B160" s="1" t="s">
+      <c r="H242" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>423</v>
+      </c>
+      <c r="B243" s="6">
+        <v>880102</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H243" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>423</v>
+      </c>
+      <c r="B244" s="6">
+        <v>880107</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H244" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>423</v>
+      </c>
+      <c r="B245" s="6">
+        <v>880107</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H245" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>423</v>
+      </c>
+      <c r="B246" s="6">
+        <v>880107</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H246" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>423</v>
+      </c>
+      <c r="B247" s="6">
+        <v>880107</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H247" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>423</v>
+      </c>
+      <c r="B248" s="6">
+        <v>880108</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H248" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>423</v>
+      </c>
+      <c r="B249" s="6">
+        <v>880108</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H249" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>2016</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D250" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D160" s="6">
-        <v>10803</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
-        <v>10803</v>
-      </c>
-      <c r="B161" s="1" t="s">
+      <c r="E250" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>2016</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D161" s="6">
-        <v>10803</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>109</v>
+      <c r="E251" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>2016</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H252" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>2016</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H253" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{C5B36CAD-FD0A-4B42-A5F0-CEDAE9F551CA}"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H236">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6044,7 +8924,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF944944-0844-4FB8-99F2-9DEC0D345698}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="11" bestFit="1" customWidth="1"/>
@@ -6055,342 +8935,430 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
-        <v>330</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="C2" s="10">
-        <v>57901</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>323</v>
+      <c r="A2">
+        <v>302</v>
+      </c>
+      <c r="B2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C2">
+        <v>59002</v>
+      </c>
+      <c r="D2" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>562</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="C3" s="10">
-        <v>57068</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>325</v>
+      <c r="A3">
+        <v>315</v>
+      </c>
+      <c r="B3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C3">
+        <v>62115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
-        <v>762</v>
+        <v>330</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C4" s="10">
-        <v>7546</v>
+        <v>57901</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <v>1416</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="C5" s="10">
-        <v>56565</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>329</v>
+      <c r="A5">
+        <v>335</v>
+      </c>
+      <c r="B5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C5">
+        <v>62116</v>
+      </c>
+      <c r="D5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
-        <v>2709</v>
+        <v>562</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C6" s="10">
-        <v>58215</v>
+        <v>57068</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>2713</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="C7" s="10">
-        <v>58697</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>333</v>
+      <c r="A7">
+        <v>613</v>
+      </c>
+      <c r="B7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C7">
+        <v>65978</v>
+      </c>
+      <c r="D7" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
-        <v>4076</v>
+        <v>762</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C8" s="10">
-        <v>7799</v>
+        <v>7546</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
-        <v>7254</v>
+        <v>1416</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="C9" s="10">
-        <v>7294</v>
+        <v>56565</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
-        <v>7258</v>
+        <v>2709</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C10" s="10">
-        <v>7268</v>
+        <v>58215</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>7762</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="C11" s="10">
-        <v>55545</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>341</v>
+      <c r="A11">
+        <v>2709</v>
+      </c>
+      <c r="B11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C11">
+        <v>7538</v>
+      </c>
+      <c r="D11" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
-        <v>7765</v>
+        <v>2713</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C12" s="10">
-        <v>7709</v>
+        <v>58697</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>10474</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="C13" s="10">
-        <v>10397</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>345</v>
+      <c r="A13">
+        <v>3612</v>
+      </c>
+      <c r="B13" t="s">
+        <v>479</v>
+      </c>
+      <c r="C13">
+        <v>7512</v>
+      </c>
+      <c r="D13" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
-        <v>10474</v>
+        <v>4076</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C14" s="10">
-        <v>54995</v>
+        <v>7799</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>10619</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="C15" s="10">
-        <v>7784</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>348</v>
+      <c r="A15" s="11">
+        <v>7146</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C15" s="11">
+        <v>2518</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
-        <v>50030</v>
+        <v>7254</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C16" s="10">
-        <v>1393</v>
+        <v>7294</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
-        <v>55120</v>
+        <v>7258</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C17" s="10">
-        <v>10789</v>
+        <v>7268</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
-        <v>55306</v>
+        <v>7762</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="C18" s="10">
-        <v>59338</v>
+        <v>55545</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
-        <v>55306</v>
+        <v>7765</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="C19" s="10">
-        <v>59784</v>
+        <v>7709</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <v>55375</v>
+        <v>10474</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="C20" s="10">
-        <v>57664</v>
+        <v>10397</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
-        <v>55481</v>
+        <v>10474</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C21" s="10">
-        <v>58557</v>
+        <v>54995</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>55508</v>
+        <v>10619</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="C22" s="10">
-        <v>55874</v>
+        <v>7784</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
+        <v>50030</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C23" s="10">
+        <v>1393</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>55120</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="C24" s="10">
+        <v>10789</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
+        <v>55306</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="10">
+        <v>59338</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
+        <v>55306</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="10">
+        <v>59784</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>55375</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C27" s="10">
+        <v>57664</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
+        <v>55481</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C28" s="10">
+        <v>58557</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>55508</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" s="10">
+        <v>55874</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
         <v>70454</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="C23" s="10">
+      <c r="B30" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" s="10">
         <v>54538</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
-        <v>7146</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C24" s="11">
-        <v>2518</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>401</v>
+      <c r="D30" s="12" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{23DBA6EA-2935-43AA-81F4-2A228D9D9EA2}"/>
+  <autoFilter ref="A1:D1" xr:uid="{23DBA6EA-2935-43AA-81F4-2A228D9D9EA2}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D30">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6411,13 +9379,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -6437,10 +9405,10 @@
         <v>1702</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6448,10 +9416,10 @@
         <v>1702</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6467,7 +9435,7 @@
         <v>2503</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6475,7 +9443,7 @@
         <v>2503</v>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6483,7 +9451,7 @@
         <v>2503</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6491,7 +9459,7 @@
         <v>2503</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6499,7 +9467,7 @@
         <v>2503</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6507,7 +9475,7 @@
         <v>2828</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6515,7 +9483,7 @@
         <v>2828</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6523,7 +9491,7 @@
         <v>3148</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6531,7 +9499,7 @@
         <v>3149</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6539,7 +9507,7 @@
         <v>3149</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6547,7 +9515,7 @@
         <v>3399</v>
       </c>
       <c r="B15" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6555,7 +9523,7 @@
         <v>3399</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -6563,7 +9531,7 @@
         <v>3406</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6571,7 +9539,7 @@
         <v>3406</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -6579,7 +9547,7 @@
         <v>3935</v>
       </c>
       <c r="B19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -6587,7 +9555,7 @@
         <v>3935</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -6595,7 +9563,7 @@
         <v>3948</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -6603,7 +9571,7 @@
         <v>6019</v>
       </c>
       <c r="B22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -6611,7 +9579,7 @@
         <v>6019</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -6619,7 +9587,7 @@
         <v>6166</v>
       </c>
       <c r="B24" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -6627,7 +9595,7 @@
         <v>6166</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -6635,7 +9603,7 @@
         <v>6264</v>
       </c>
       <c r="B26" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -6643,7 +9611,7 @@
         <v>6264</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -6651,7 +9619,7 @@
         <v>7737</v>
       </c>
       <c r="B28" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -6659,7 +9627,7 @@
         <v>7737</v>
       </c>
       <c r="B29" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -6667,7 +9635,7 @@
         <v>7737</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -6675,7 +9643,7 @@
         <v>8102</v>
       </c>
       <c r="B31" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -6683,7 +9651,7 @@
         <v>8102</v>
       </c>
       <c r="B32" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -6691,7 +9659,7 @@
         <v>10474</v>
       </c>
       <c r="B33" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -6699,7 +9667,7 @@
         <v>10474</v>
       </c>
       <c r="B34" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -6707,7 +9675,7 @@
         <v>10474</v>
       </c>
       <c r="B35" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -6715,7 +9683,7 @@
         <v>10474</v>
       </c>
       <c r="B36" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -6723,7 +9691,7 @@
         <v>10474</v>
       </c>
       <c r="B37" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -6731,7 +9699,7 @@
         <v>10474</v>
       </c>
       <c r="B38" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -6739,7 +9707,7 @@
         <v>10474</v>
       </c>
       <c r="B39" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -6747,7 +9715,7 @@
         <v>10788</v>
       </c>
       <c r="B40" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -6755,7 +9723,7 @@
         <v>10865</v>
       </c>
       <c r="B41" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -6763,7 +9731,7 @@
         <v>10865</v>
       </c>
       <c r="B42" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -6787,7 +9755,7 @@
         <v>10867</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -6795,7 +9763,7 @@
         <v>10867</v>
       </c>
       <c r="B46" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -6803,7 +9771,7 @@
         <v>50044</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -6811,7 +9779,7 @@
         <v>50151</v>
       </c>
       <c r="B48" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -6819,7 +9787,7 @@
         <v>50151</v>
       </c>
       <c r="B49" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -6827,7 +9795,7 @@
         <v>50188</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -6875,7 +9843,7 @@
         <v>50244</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -6883,7 +9851,7 @@
         <v>50244</v>
       </c>
       <c r="B57" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -6891,7 +9859,7 @@
         <v>50244</v>
       </c>
       <c r="B58" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -6899,7 +9867,7 @@
         <v>50244</v>
       </c>
       <c r="B59" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -6907,7 +9875,7 @@
         <v>50244</v>
       </c>
       <c r="B60" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -6915,7 +9883,7 @@
         <v>50472</v>
       </c>
       <c r="B61" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -6931,7 +9899,7 @@
         <v>50481</v>
       </c>
       <c r="B63" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -6939,7 +9907,7 @@
         <v>50607</v>
       </c>
       <c r="B64" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -6947,7 +9915,7 @@
         <v>50607</v>
       </c>
       <c r="B65" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -6955,7 +9923,7 @@
         <v>50607</v>
       </c>
       <c r="B66" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -6963,7 +9931,7 @@
         <v>50607</v>
       </c>
       <c r="B67" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -6971,7 +9939,7 @@
         <v>50607</v>
       </c>
       <c r="B68" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -6979,7 +9947,7 @@
         <v>50627</v>
       </c>
       <c r="B69" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -6987,7 +9955,7 @@
         <v>50628</v>
       </c>
       <c r="B70" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -6995,7 +9963,7 @@
         <v>50729</v>
       </c>
       <c r="B71" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7003,7 +9971,7 @@
         <v>50729</v>
       </c>
       <c r="B72" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7011,7 +9979,7 @@
         <v>50733</v>
       </c>
       <c r="B73" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7019,7 +9987,7 @@
         <v>50733</v>
       </c>
       <c r="B74" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7027,7 +9995,7 @@
         <v>50733</v>
       </c>
       <c r="B75" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7035,7 +10003,7 @@
         <v>50733</v>
       </c>
       <c r="B76" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7043,7 +10011,7 @@
         <v>50733</v>
       </c>
       <c r="B77" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7051,7 +10019,7 @@
         <v>50733</v>
       </c>
       <c r="B78" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7059,7 +10027,7 @@
         <v>50733</v>
       </c>
       <c r="B79" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7067,7 +10035,7 @@
         <v>50733</v>
       </c>
       <c r="B80" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -7083,7 +10051,7 @@
         <v>50900</v>
       </c>
       <c r="B82" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -7091,7 +10059,7 @@
         <v>50900</v>
       </c>
       <c r="B83" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -7099,7 +10067,7 @@
         <v>50900</v>
       </c>
       <c r="B84" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -7123,7 +10091,7 @@
         <v>50965</v>
       </c>
       <c r="B87" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -7131,7 +10099,7 @@
         <v>50965</v>
       </c>
       <c r="B88" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -7139,7 +10107,7 @@
         <v>50965</v>
       </c>
       <c r="B89" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -7147,7 +10115,7 @@
         <v>52089</v>
       </c>
       <c r="B90" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -7155,7 +10123,7 @@
         <v>52089</v>
       </c>
       <c r="B91" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -7163,7 +10131,7 @@
         <v>52089</v>
       </c>
       <c r="B92" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -7171,7 +10139,7 @@
         <v>52089</v>
       </c>
       <c r="B93" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -7179,7 +10147,7 @@
         <v>52089</v>
       </c>
       <c r="B94" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -7187,7 +10155,7 @@
         <v>52168</v>
       </c>
       <c r="B95" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -7195,7 +10163,7 @@
         <v>52193</v>
       </c>
       <c r="B96" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -7203,7 +10171,7 @@
         <v>52193</v>
       </c>
       <c r="B97" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -7211,7 +10179,7 @@
         <v>52193</v>
       </c>
       <c r="B98" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -7219,7 +10187,7 @@
         <v>52193</v>
       </c>
       <c r="B99" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -7227,7 +10195,7 @@
         <v>52193</v>
       </c>
       <c r="B100" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -7235,7 +10203,7 @@
         <v>52193</v>
       </c>
       <c r="B101" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -7243,7 +10211,7 @@
         <v>52193</v>
       </c>
       <c r="B102" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -7251,7 +10219,7 @@
         <v>52193</v>
       </c>
       <c r="B103" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -7259,7 +10227,7 @@
         <v>54276</v>
       </c>
       <c r="B104" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -7267,7 +10235,7 @@
         <v>55216</v>
       </c>
       <c r="B105" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -7275,7 +10243,7 @@
         <v>55216</v>
       </c>
       <c r="B106" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -7283,7 +10251,7 @@
         <v>55308</v>
       </c>
       <c r="B107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -7291,7 +10259,7 @@
         <v>55308</v>
       </c>
       <c r="B108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -7299,7 +10267,7 @@
         <v>55386</v>
       </c>
       <c r="B109" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -7307,7 +10275,7 @@
         <v>55386</v>
       </c>
       <c r="B110" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -7315,7 +10283,7 @@
         <v>55386</v>
       </c>
       <c r="B111" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -7323,7 +10291,7 @@
         <v>55703</v>
       </c>
       <c r="B112" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -7337,47 +10305,47 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="82.7109375" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B3" s="13" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="180" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="225" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="330" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>367</v>
-      </c>
       <c r="B4" s="13" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -7387,11 +10355,59 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2021-06-22T20:59:33+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF32AD688505FB45A4B74E8374DD655E" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="820e166eda12a2b21727580e35d4b1c4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="03c14dc6-992a-47d3-9648-df74221fc344" xmlns:ns6="434a65cb-19a2-4f64-81f9-c4c3497f5b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73bb20789afc0d8257071bd90159119b" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7828,55 +10844,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2021-06-22T20:59:33+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F48335-9609-4D38-B63B-9A6620FE759C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="434a65cb-19a2-4f64-81f9-c4c3497f5b4c"/>
+    <ds:schemaRef ds:uri="03c14dc6-992a-47d3-9648-df74221fc344"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D1F9EA-526B-4162-847E-36B5EC9F2951}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B99ED44-03A6-4635-B387-C99415CE560D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
@@ -7884,7 +10881,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D1E071-1F27-41E0-9A83-EBB1CE4676B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7905,33 +10902,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F48335-9609-4D38-B63B-9A6620FE759C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="434a65cb-19a2-4f64-81f9-c4c3497f5b4c"/>
-    <ds:schemaRef ds:uri="03c14dc6-992a-47d3-9648-df74221fc344"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D1F9EA-526B-4162-847E-36B5EC9F2951}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/manual_matches.xlsx
+++ b/manual_matches.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\capd_eia_crosswalk\users\gofortht\crosswalk_repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45954162-E376-4628-91CD-EACC30ECD91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94E93B8-E055-4CA7-BC07-E057045814CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2370" yWindow="3900" windowWidth="28800" windowHeight="7800" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5460" yWindow="1170" windowWidth="28800" windowHeight="7800" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_manual_matches" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">plant_id_manual_matches!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">unit_manual_excluded!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">unit_manual_excluded!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">unit_manual_matches!$A$1:$G$74</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="497">
   <si>
     <t>EIA_PLANT_ID</t>
   </si>
@@ -1306,6 +1306,231 @@
   </si>
   <si>
     <t>BLR02C</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Only 2018</t>
+  </si>
+  <si>
+    <t>Not grid connected.</t>
+  </si>
+  <si>
+    <t>H8</t>
+  </si>
+  <si>
+    <t>H9</t>
+  </si>
+  <si>
+    <t>Retired</t>
+  </si>
+  <si>
+    <t>Retired in 2019</t>
+  </si>
+  <si>
+    <t>**2A</t>
+  </si>
+  <si>
+    <t>**2B</t>
+  </si>
+  <si>
+    <t>1SG</t>
+  </si>
+  <si>
+    <t>002001</t>
+  </si>
+  <si>
+    <t>EUBHB9</t>
+  </si>
+  <si>
+    <t>BLR08</t>
+  </si>
+  <si>
+    <t>PR003</t>
+  </si>
+  <si>
+    <t>PR004</t>
+  </si>
+  <si>
+    <t>PR005</t>
+  </si>
+  <si>
+    <t>AAB01</t>
+  </si>
+  <si>
+    <t>150137</t>
+  </si>
+  <si>
+    <t>150138</t>
+  </si>
+  <si>
+    <t>150139</t>
+  </si>
+  <si>
+    <t>150140</t>
+  </si>
+  <si>
+    <t>150145</t>
+  </si>
+  <si>
+    <t>CT1</t>
+  </si>
+  <si>
+    <t>DES1</t>
+  </si>
+  <si>
+    <t>DES2</t>
+  </si>
+  <si>
+    <t>CTP</t>
+  </si>
+  <si>
+    <t>214JA</t>
+  </si>
+  <si>
+    <t>214JB</t>
+  </si>
+  <si>
+    <t>B921A</t>
+  </si>
+  <si>
+    <t>5STA</t>
+  </si>
+  <si>
+    <t>5STB</t>
+  </si>
+  <si>
+    <t>B921B</t>
+  </si>
+  <si>
+    <t>GT501A</t>
+  </si>
+  <si>
+    <t>GT501B</t>
+  </si>
+  <si>
+    <t>5B921A</t>
+  </si>
+  <si>
+    <t>5B921B</t>
+  </si>
+  <si>
+    <t>5L501A</t>
+  </si>
+  <si>
+    <t>5L501B</t>
+  </si>
+  <si>
+    <t>Retired in 2019 and not in EIA data at all</t>
+  </si>
+  <si>
+    <t>Not operating since 2019</t>
+  </si>
+  <si>
+    <t>In Long Term Cold Storage (LTCS), not in 860 or 923</t>
+  </si>
+  <si>
+    <t>Closed in 2020 not in 860 or 923</t>
+  </si>
+  <si>
+    <t>Retired and not in 860 or 923</t>
+  </si>
+  <si>
+    <t>Not operating in 2021</t>
+  </si>
+  <si>
+    <t>Partially retired in 2019 and partially not connected to the grid. Not in EIA at all</t>
+  </si>
+  <si>
+    <t>LTCS in 2019 and not in EIA data at all</t>
+  </si>
+  <si>
+    <t>In Long Term Cold Storage, not in 860 or 923</t>
+  </si>
+  <si>
+    <t>Cabrillo Power I Encina Power Station</t>
+  </si>
+  <si>
+    <t>AES Alamitos</t>
+  </si>
+  <si>
+    <t>Carlsbad Energy Center</t>
+  </si>
+  <si>
+    <t>AES Alamitos Energy Center</t>
+  </si>
+  <si>
+    <t>AES Huntington Beach</t>
+  </si>
+  <si>
+    <t>AES Huntington Beach Energy Project</t>
+  </si>
+  <si>
+    <t>Lauderdale</t>
+  </si>
+  <si>
+    <t>Dania Beach 7</t>
+  </si>
+  <si>
+    <t>Wayne County</t>
+  </si>
+  <si>
+    <t>V H Braunig</t>
+  </si>
+  <si>
+    <t>Arthur Von Rosenberg</t>
+  </si>
+  <si>
+    <t>AG1</t>
+  </si>
+  <si>
+    <t>AG2</t>
+  </si>
+  <si>
+    <t>COS3</t>
+  </si>
+  <si>
+    <t>COS4</t>
+  </si>
+  <si>
+    <t>COS5</t>
+  </si>
+  <si>
+    <t>COS6</t>
+  </si>
+  <si>
+    <t>SJ10</t>
+  </si>
+  <si>
+    <t>SJ7</t>
+  </si>
+  <si>
+    <t>SJ8</t>
+  </si>
+  <si>
+    <t>SJ9</t>
+  </si>
+  <si>
+    <t>PS1</t>
+  </si>
+  <si>
+    <t>PS2</t>
+  </si>
+  <si>
+    <t>PS3</t>
+  </si>
+  <si>
+    <t>PS4</t>
+  </si>
+  <si>
+    <t>UNIT1</t>
+  </si>
+  <si>
+    <t>UNIT2</t>
   </si>
 </sst>
 </file>
@@ -2213,7 +2438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -3795,6 +4020,230 @@
         <v>399</v>
       </c>
     </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>880102</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="6">
+        <v>61082</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>880102</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2</v>
+      </c>
+      <c r="D76" s="6">
+        <v>61082</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>880105</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D77" s="6">
+        <v>61146</v>
+      </c>
+      <c r="F77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>880105</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D78" s="6">
+        <v>61146</v>
+      </c>
+      <c r="F78" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>880104</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D79" s="6">
+        <v>61147</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>880104</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D80" s="6">
+        <v>61147</v>
+      </c>
+      <c r="E80" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>880104</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D81" s="6">
+        <v>61147</v>
+      </c>
+      <c r="E81" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>880104</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D82" s="6">
+        <v>61147</v>
+      </c>
+      <c r="E82" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>880106</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D83" s="6">
+        <v>61148</v>
+      </c>
+      <c r="E83" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>880106</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D84" s="6">
+        <v>61148</v>
+      </c>
+      <c r="E84" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>880107</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D85" s="6">
+        <v>61148</v>
+      </c>
+      <c r="E85" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>880108</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D86" s="6">
+        <v>61148</v>
+      </c>
+      <c r="E86" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>880103</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D87" s="6">
+        <v>61149</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>880103</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D88" s="6">
+        <v>61149</v>
+      </c>
+      <c r="E88" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>880103</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D89" s="6">
+        <v>61149</v>
+      </c>
+      <c r="E89" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>880103</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D90" s="6">
+        <v>61149</v>
+      </c>
+      <c r="E90" s="1">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G74" xr:uid="{AA9693D4-94E9-4250-828A-FAABB27742CD}"/>
   <phoneticPr fontId="20" type="noConversion"/>
@@ -3805,2631 +4254,4666 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="6">
+        <v>127</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2">
+        <v>127</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2012</v>
+      </c>
+      <c r="B3" s="6">
         <v>228</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E3" s="1">
         <v>228</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F3" s="1">
         <v>10</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G3" s="1">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4" s="6">
         <v>228</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E4" s="1">
         <v>228</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F4" s="1">
         <v>9</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G4" s="1">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2012</v>
+      </c>
+      <c r="B5" s="6">
         <v>259</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E5" s="3">
         <v>259</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2012</v>
+      </c>
+      <c r="B6" s="6">
         <v>259</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E6" s="3">
         <v>259</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H6" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2012</v>
+      </c>
+      <c r="B7" s="6">
         <v>259</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E7" s="3">
         <v>259</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2012</v>
+      </c>
+      <c r="B8" s="6">
         <v>259</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E8" s="3">
         <v>259</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H8" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2012</v>
+      </c>
+      <c r="B9" s="6">
         <v>271</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="3">
+      <c r="E9" s="3">
         <v>271</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F9" s="1">
         <v>5</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G9" s="1">
         <v>5</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H9" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2012</v>
+      </c>
+      <c r="B10" s="6">
         <v>271</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="3">
+      <c r="E10" s="3">
         <v>271</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F10" s="1">
         <v>6</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G10" s="1">
         <v>6</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2012</v>
+      </c>
+      <c r="B11" s="6">
         <v>271</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="3">
+      <c r="E11" s="3">
         <v>271</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F11" s="1">
         <v>7</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G11" s="1">
         <v>7</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H11" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2010</v>
+      </c>
+      <c r="B12" s="6">
         <v>273</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="3">
+      <c r="E12" s="3">
         <v>273</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G12" s="1">
         <v>3</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2010</v>
+      </c>
+      <c r="B13" s="2">
         <v>310</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E13" s="2">
         <v>310</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2010</v>
+      </c>
+      <c r="B14" s="2">
         <v>310</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E14" s="2">
         <v>310</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2010</v>
+      </c>
+      <c r="B15" s="2">
         <v>356</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2018</v>
+      </c>
+      <c r="B16" s="2">
         <v>389</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E16" s="2">
         <v>389</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="6">
+        <v>478</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1">
+        <v>478</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2016</v>
+      </c>
+      <c r="B18" s="6">
+        <v>478</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1">
+        <v>478</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2016</v>
+      </c>
+      <c r="B19" s="6">
+        <v>478</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1">
+        <v>478</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2021</v>
+      </c>
+      <c r="B20" s="6">
+        <v>764</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E20" s="6">
+        <v>764</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2021</v>
+      </c>
+      <c r="B21" s="6">
+        <v>764</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E21" s="6">
+        <v>764</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1552</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1552</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2020</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1552</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1552</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2016</v>
+      </c>
+      <c r="B24" s="7">
         <v>1594</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="E24" s="3"/>
+      <c r="G24" s="4"/>
+      <c r="H24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2016</v>
+      </c>
+      <c r="B25" s="7">
         <v>1594</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="F17" s="4"/>
-      <c r="G17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>1594</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>2440</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="G24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>116</v>
+      <c r="D25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="G25" s="4"/>
+      <c r="H25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2016</v>
+      </c>
+      <c r="B26" s="7">
+        <v>1594</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>2504</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>117</v>
+      <c r="D26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2016</v>
+      </c>
+      <c r="B27" s="7">
+        <v>1594</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" t="s">
+      <c r="D27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2016</v>
+      </c>
+      <c r="B28" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2016</v>
+      </c>
+      <c r="B29" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2016</v>
+      </c>
+      <c r="B30" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2016</v>
+      </c>
+      <c r="B31" s="7">
+        <v>1594</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2016</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2440</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="H32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2005</v>
+      </c>
+      <c r="B33" s="7">
+        <v>2504</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2005</v>
+      </c>
+      <c r="B34" s="7">
+        <v>2504</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2005</v>
+      </c>
+      <c r="B35" s="7">
+        <v>2504</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2020</v>
+      </c>
+      <c r="B36" s="6">
+        <v>2535</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2535</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2020</v>
+      </c>
+      <c r="B37" s="6">
+        <v>2535</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2535</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2018</v>
+      </c>
+      <c r="B38" s="7">
         <v>2549</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" t="s">
+      <c r="E38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2018</v>
+      </c>
+      <c r="B39" s="7">
         <v>2549</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" t="s">
+      <c r="E39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2021</v>
+      </c>
+      <c r="B40" s="6">
+        <v>2837</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="6">
+        <v>2837</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2020</v>
+      </c>
+      <c r="B41" s="6">
+        <v>3344</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3344</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2020</v>
+      </c>
+      <c r="B42" s="6">
+        <v>3344</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3344</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2022</v>
+      </c>
+      <c r="B43" s="6">
+        <v>3946</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="6">
+        <v>3946</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2022</v>
+      </c>
+      <c r="B44" s="6">
+        <v>3946</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="6">
+        <v>3946</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2021</v>
+      </c>
+      <c r="B45" s="6">
+        <v>6082</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="6">
+        <v>6082</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2021</v>
+      </c>
+      <c r="B46" s="6">
+        <v>6094</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="1">
+        <v>6094</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2021</v>
+      </c>
+      <c r="B47" s="6">
+        <v>6094</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="1">
+        <v>6094</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2021</v>
+      </c>
+      <c r="B48" s="6">
+        <v>6094</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="1">
+        <v>6094</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2021</v>
+      </c>
+      <c r="B49" s="6">
+        <v>6106</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1">
+        <v>6106</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2020</v>
+      </c>
+      <c r="B50" s="6">
+        <v>6136</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="6">
+        <v>6136</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2023</v>
+      </c>
+      <c r="B51" s="6">
+        <v>6776</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="6">
+        <v>6776</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2018</v>
+      </c>
+      <c r="B52" s="2">
         <v>10071</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G30" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="H52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2018</v>
+      </c>
+      <c r="B53" s="2">
         <v>10071</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G31" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="H53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2018</v>
+      </c>
+      <c r="B54" s="2">
         <v>10071</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="H54" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2018</v>
+      </c>
+      <c r="B55" s="2">
         <v>10071</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G33" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="H55" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2018</v>
+      </c>
+      <c r="B56" s="2">
         <v>10071</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G34" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="H56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2018</v>
+      </c>
+      <c r="B57" s="2">
         <v>10071</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G35" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
+      <c r="H57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2016</v>
+      </c>
+      <c r="B58" s="6">
+        <v>10111</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2021</v>
+      </c>
+      <c r="B59" s="6">
+        <v>10350</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="6">
+        <v>10350</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H59" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2021</v>
+      </c>
+      <c r="B60" s="6">
+        <v>10350</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="6">
+        <v>10350</v>
+      </c>
+      <c r="F60"/>
+      <c r="G60" t="s">
+        <v>71</v>
+      </c>
+      <c r="H60" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2016</v>
+      </c>
+      <c r="B61" s="6">
+        <v>10381</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H61" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2016</v>
+      </c>
+      <c r="B62" s="6">
+        <v>10381</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2020</v>
+      </c>
+      <c r="B63" s="6">
+        <v>10384</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="1">
+        <v>10384</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H63" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2020</v>
+      </c>
+      <c r="B64" s="6">
+        <v>10384</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="1">
+        <v>10384</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H64" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2020</v>
+      </c>
+      <c r="B65" s="6">
+        <v>10384</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E65" s="1">
+        <v>10384</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H65" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2020</v>
+      </c>
+      <c r="B66" s="6">
+        <v>10384</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" s="1">
+        <v>10384</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H66" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2016</v>
+      </c>
+      <c r="B67" s="8">
         <v>10675</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
+      <c r="E67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2016</v>
+      </c>
+      <c r="B68" s="8">
         <v>10675</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="E68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2023</v>
+      </c>
+      <c r="B69" s="6">
+        <v>10698</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="6">
+        <v>10698</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2016</v>
+      </c>
+      <c r="B70" s="2">
         <v>10788</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="G38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="D70" s="2"/>
+      <c r="H70" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2007</v>
+      </c>
+      <c r="B71" s="6">
         <v>10803</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D39" s="6">
+      <c r="E71" s="6">
         <v>10803</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="G71" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="H71" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2007</v>
+      </c>
+      <c r="B72" s="6">
         <v>10803</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D40" s="6">
+      <c r="E72" s="6">
         <v>10803</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2016</v>
+      </c>
+      <c r="B73" s="2">
         <v>50044</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="G41" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="D73" s="2"/>
+      <c r="H73" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2021</v>
+      </c>
+      <c r="B74">
+        <v>50137</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74">
+        <v>50137</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2016</v>
+      </c>
+      <c r="B75" s="2">
         <v>50151</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="H75" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2016</v>
+      </c>
+      <c r="B76" s="2">
         <v>50151</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G43" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="H76" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2018</v>
+      </c>
+      <c r="B77" s="2">
         <v>50202</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G44" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="H77" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2016</v>
+      </c>
+      <c r="B78">
+        <v>50247</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H78" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2016</v>
+      </c>
+      <c r="B79">
+        <v>50247</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H79" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2016</v>
+      </c>
+      <c r="B80">
+        <v>50247</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H80" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2016</v>
+      </c>
+      <c r="B81">
+        <v>50247</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2020</v>
+      </c>
+      <c r="B82">
+        <v>50282</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82">
+        <v>50282</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H82" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2020</v>
+      </c>
+      <c r="B83">
+        <v>50282</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E83">
+        <v>50282</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H83" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2020</v>
+      </c>
+      <c r="B84">
+        <v>50282</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84">
+        <v>50282</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H84" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2020</v>
+      </c>
+      <c r="B85">
+        <v>50282</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E85">
+        <v>50282</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H85" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2020</v>
+      </c>
+      <c r="B86">
+        <v>50282</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86">
+        <v>50282</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H86" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2020</v>
+      </c>
+      <c r="B87">
+        <v>50282</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E87">
+        <v>50282</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H87" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2016</v>
+      </c>
+      <c r="B88" s="2">
         <v>50607</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="G45" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="D88" s="2"/>
+      <c r="H88" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2016</v>
+      </c>
+      <c r="B89" s="2">
         <v>50607</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="G46" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="D89" s="2"/>
+      <c r="H89" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>2016</v>
+      </c>
+      <c r="B90" s="2">
         <v>50607</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="G47" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="D90" s="2"/>
+      <c r="H90" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2016</v>
+      </c>
+      <c r="B91" s="2">
         <v>50607</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C91" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="G48" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="D91" s="2"/>
+      <c r="H91" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>2016</v>
+      </c>
+      <c r="B92" s="2">
         <v>50607</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C92" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="G49" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="D92" s="2"/>
+      <c r="H92" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>2023</v>
+      </c>
+      <c r="B93">
+        <v>50852</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93">
+        <v>50852</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>2023</v>
+      </c>
+      <c r="B94">
+        <v>50852</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E94">
+        <v>50852</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>2021</v>
+      </c>
+      <c r="B95">
+        <v>50976</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95">
+        <v>50976</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>2010</v>
+      </c>
+      <c r="B96" s="2">
         <v>51000</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D96" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="G96" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="H96" s="1" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>2020</v>
+      </c>
+      <c r="B97">
+        <v>52106</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H97" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>2020</v>
+      </c>
+      <c r="B98">
+        <v>52106</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="H98" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>2020</v>
+      </c>
+      <c r="B99">
+        <v>52106</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H99" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>2020</v>
+      </c>
+      <c r="B100">
+        <v>52106</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H100" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>2020</v>
+      </c>
+      <c r="B101">
+        <v>52106</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H101" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2018</v>
+      </c>
+      <c r="B102" s="2">
         <v>54035</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G51" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="H102" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2016</v>
+      </c>
+      <c r="B103" s="6">
         <v>54571</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D52" s="6">
+      <c r="E103" s="6">
         <v>54571</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G103" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="H103" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>2016</v>
+      </c>
+      <c r="B104" s="6">
         <v>54571</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D53" s="6">
+      <c r="E104" s="6">
         <v>54571</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="G104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H104" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>2016</v>
+      </c>
+      <c r="B105" s="6">
         <v>54571</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="6">
+      <c r="E105" s="6">
         <v>54571</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="G105" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H105" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>2016</v>
+      </c>
+      <c r="B106" s="6">
         <v>54571</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D55" s="6">
+      <c r="E106" s="6">
         <v>54571</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="G106" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="H106" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>2016</v>
+      </c>
+      <c r="B107" s="2">
         <v>54571</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="H107" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>2016</v>
+      </c>
+      <c r="B108" s="2">
         <v>54571</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="H108" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>2016</v>
+      </c>
+      <c r="B109" s="2">
         <v>54571</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G58" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="H109" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>2016</v>
+      </c>
+      <c r="B110" s="2">
         <v>54571</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G59" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="H110" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>2018</v>
+      </c>
+      <c r="B111" s="2">
         <v>54755</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D111" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G60" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
+      <c r="H111" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>2018</v>
+      </c>
+      <c r="B112" s="6">
         <v>55098</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="H112" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>2018</v>
+      </c>
+      <c r="B113" s="6">
         <v>55098</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="H113" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>2018</v>
+      </c>
+      <c r="B114" s="6">
         <v>55098</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="H114" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>2018</v>
+      </c>
+      <c r="B115" s="6">
         <v>55098</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="H115" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>2018</v>
+      </c>
+      <c r="B116" s="2">
         <v>55098</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G65" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="H116" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>2018</v>
+      </c>
+      <c r="B117" s="2">
         <v>55098</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="D117" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G66" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="H117" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>2018</v>
+      </c>
+      <c r="B118" s="2">
         <v>55098</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C118" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="D118" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G67" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="H118" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>2018</v>
+      </c>
+      <c r="B119" s="2">
         <v>55098</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D119" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G68" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="H119" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>2016</v>
+      </c>
+      <c r="B120">
+        <v>55422</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="H120" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>2016</v>
+      </c>
+      <c r="B121">
+        <v>55422</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H121" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>424</v>
+      </c>
+      <c r="B122" s="6">
         <v>55524</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C122" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="H122" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>424</v>
+      </c>
+      <c r="B123" s="6">
         <v>55524</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C123" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="H123" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>424</v>
+      </c>
+      <c r="B124" s="6">
         <v>55524</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="H124" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>424</v>
+      </c>
+      <c r="B125" s="6">
         <v>55524</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C125" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="H125" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>2018</v>
+      </c>
+      <c r="B126" s="6">
         <v>55699</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C126" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H126" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>2016</v>
+      </c>
+      <c r="B127" s="2">
         <v>55703</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C74" s="2"/>
-      <c r="G74" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
+      <c r="D127" s="2"/>
+      <c r="H127" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>2020</v>
+      </c>
+      <c r="B128">
+        <v>55833</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H128" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>2021</v>
+      </c>
+      <c r="B129">
+        <v>59073</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E129" s="1">
+        <v>59073</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>2021</v>
+      </c>
+      <c r="B130">
+        <v>59073</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E130" s="1">
+        <v>59073</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>2021</v>
+      </c>
+      <c r="B131">
+        <v>59073</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E131" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>2021</v>
+      </c>
+      <c r="B132">
+        <v>59073</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E132" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>2021</v>
+      </c>
+      <c r="B133">
+        <v>59073</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E133" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>2021</v>
+      </c>
+      <c r="B134">
+        <v>59073</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E134" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>2021</v>
+      </c>
+      <c r="B135">
+        <v>59073</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E135" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>2021</v>
+      </c>
+      <c r="B136">
+        <v>59073</v>
+      </c>
+      <c r="C136" t="s">
+        <v>455</v>
+      </c>
+      <c r="D136" t="s">
+        <v>453</v>
+      </c>
+      <c r="E136">
+        <v>59073</v>
+      </c>
+      <c r="F136" t="s">
+        <v>459</v>
+      </c>
+      <c r="G136" t="s">
+        <v>453</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>2021</v>
+      </c>
+      <c r="B137">
+        <v>59073</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E137" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>2021</v>
+      </c>
+      <c r="B138">
+        <v>59073</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E138" s="1">
+        <v>59073</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>2018</v>
+      </c>
+      <c r="B139" s="6">
         <v>60345</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C139" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D75" s="6">
+      <c r="E139" s="6">
         <v>60345</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="G139" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="H139" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>2018</v>
+      </c>
+      <c r="B140" s="6">
         <v>60345</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C140" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D76" s="6">
+      <c r="E140" s="6">
         <v>60345</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="G140" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="H140" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>2018</v>
+      </c>
+      <c r="B141" s="6">
         <v>60345</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C141" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D77" s="6">
+      <c r="E141" s="6">
         <v>60345</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="G141" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="H141" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>2018</v>
+      </c>
+      <c r="B142" s="6">
         <v>60345</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C142" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D78" s="6">
+      <c r="E142" s="6">
         <v>60345</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="F142" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="G142" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="H142" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>2018</v>
+      </c>
+      <c r="B143" s="6">
         <v>60345</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="C143" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D79" s="6">
+      <c r="E143" s="6">
         <v>60345</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="G143" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H143" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>2018</v>
+      </c>
+      <c r="B144" s="6">
         <v>60345</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C144" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D144" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D80" s="6">
+      <c r="E144" s="6">
         <v>60345</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="F144" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="G144" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="H144" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>423</v>
+      </c>
+      <c r="B145" s="6">
         <v>880004</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C145" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G81" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+      <c r="H145" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>423</v>
+      </c>
+      <c r="B146" s="6">
         <v>880004</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C146" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G82" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+      <c r="H146" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>423</v>
+      </c>
+      <c r="B147" s="6">
         <v>880004</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C147" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G83" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="H147" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>423</v>
+      </c>
+      <c r="B148" s="6">
         <v>880004</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G84" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="H148" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>423</v>
+      </c>
+      <c r="B149" s="6">
         <v>880004</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C149" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G85" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="H149" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>423</v>
+      </c>
+      <c r="B150" s="6">
         <v>880004</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C150" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G86" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="H150" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>423</v>
+      </c>
+      <c r="B151" s="6">
         <v>880004</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C151" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G87" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="H151" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>423</v>
+      </c>
+      <c r="B152" s="6">
         <v>880006</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="C152" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G88" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+      <c r="H152" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>423</v>
+      </c>
+      <c r="B153" s="6">
         <v>880006</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C153" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G89" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+      <c r="H153" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>423</v>
+      </c>
+      <c r="B154" s="6">
         <v>880006</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C154" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G90" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="H154" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>423</v>
+      </c>
+      <c r="B155" s="6">
         <v>880006</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G91" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="H155" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>423</v>
+      </c>
+      <c r="B156" s="6">
         <v>880007</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C156" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G92" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="H156" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>423</v>
+      </c>
+      <c r="B157" s="6">
         <v>880016</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C157" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G93" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="H157" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>423</v>
+      </c>
+      <c r="B158" s="6">
         <v>880016</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C158" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G94" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="H158" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>423</v>
+      </c>
+      <c r="B159" s="6">
         <v>880016</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C159" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G95" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="H159" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>423</v>
+      </c>
+      <c r="B160" s="6">
         <v>880023</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C160" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G96" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="H160" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>423</v>
+      </c>
+      <c r="B161" s="6">
         <v>880023</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="C161" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G97" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="H161" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>423</v>
+      </c>
+      <c r="B162" s="6">
         <v>880023</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C162" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G98" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
+      <c r="H162" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>423</v>
+      </c>
+      <c r="B163" s="6">
         <v>880023</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C163" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G99" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
+      <c r="H163" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>423</v>
+      </c>
+      <c r="B164" s="6">
         <v>880024</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C164" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G100" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
+      <c r="H164" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>423</v>
+      </c>
+      <c r="B165" s="6">
         <v>880025</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C165" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G101" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="H165" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>423</v>
+      </c>
+      <c r="B166" s="6">
         <v>880025</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C166" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G102" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="H166" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>423</v>
+      </c>
+      <c r="B167" s="6">
         <v>880025</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C167" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G103" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="H167" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>423</v>
+      </c>
+      <c r="B168" s="6">
         <v>880025</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="C168" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G104" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="H168" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>423</v>
+      </c>
+      <c r="B169" s="6">
         <v>880028</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C169" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G105" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="H169" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>423</v>
+      </c>
+      <c r="B170" s="6">
         <v>880029</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C170" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G106" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="H170" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>423</v>
+      </c>
+      <c r="B171" s="6">
         <v>880030</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C171" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G107" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="H171" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>423</v>
+      </c>
+      <c r="B172" s="6">
         <v>880030</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C172" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G108" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="H172" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>423</v>
+      </c>
+      <c r="B173" s="6">
         <v>880031</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C173" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G109" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="H173" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>423</v>
+      </c>
+      <c r="B174" s="6">
         <v>880031</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C174" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G110" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="H174" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>423</v>
+      </c>
+      <c r="B175" s="6">
         <v>880033</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C175" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G111" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="H175" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>423</v>
+      </c>
+      <c r="B176" s="6">
         <v>880038</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C176" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G112" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="6">
+      <c r="H176" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>423</v>
+      </c>
+      <c r="B177" s="6">
         <v>880039</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C177" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G113" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="6">
+      <c r="H177" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>423</v>
+      </c>
+      <c r="B178" s="6">
         <v>880039</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C178" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G114" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
+      <c r="H178" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>423</v>
+      </c>
+      <c r="B179" s="6">
         <v>880041</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="C179" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G115" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
+      <c r="H179" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>423</v>
+      </c>
+      <c r="B180" s="6">
         <v>880041</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C180" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G116" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="H180" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>423</v>
+      </c>
+      <c r="B181" s="6">
         <v>880041</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C181" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G117" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="6">
+      <c r="H181" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>423</v>
+      </c>
+      <c r="B182" s="6">
         <v>880042</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C182" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G118" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="6">
+      <c r="H182" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>423</v>
+      </c>
+      <c r="B183" s="6">
         <v>880042</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C183" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G119" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
+      <c r="H183" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>423</v>
+      </c>
+      <c r="B184" s="6">
         <v>880042</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C184" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G120" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="6">
+      <c r="H184" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>423</v>
+      </c>
+      <c r="B185" s="6">
         <v>880042</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C185" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G121" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="6">
+      <c r="H185" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>423</v>
+      </c>
+      <c r="B186" s="6">
         <v>880043</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C186" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G122" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="6">
+      <c r="H186" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>423</v>
+      </c>
+      <c r="B187" s="6">
         <v>880044</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C187" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="G123" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
+      <c r="H187" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>423</v>
+      </c>
+      <c r="B188" s="6">
         <v>880045</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C188" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="G124" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="6">
+      <c r="H188" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>423</v>
+      </c>
+      <c r="B189" s="6">
         <v>880045</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="C189" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G125" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="6">
+      <c r="H189" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>423</v>
+      </c>
+      <c r="B190" s="6">
         <v>880045</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="C190" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G126" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="6">
+      <c r="H190" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>423</v>
+      </c>
+      <c r="B191" s="6">
         <v>880049</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C191" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G127" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
+      <c r="H191" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>423</v>
+      </c>
+      <c r="B192" s="6">
         <v>880050</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C192" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G128" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="6">
+      <c r="H192" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>423</v>
+      </c>
+      <c r="B193" s="6">
         <v>880052</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C193" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G129" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
+      <c r="H193" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>423</v>
+      </c>
+      <c r="B194" s="6">
         <v>880053</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C194" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G130" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="6">
+      <c r="H194" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>423</v>
+      </c>
+      <c r="B195" s="6">
         <v>880053</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C195" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G131" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
+      <c r="H195" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>423</v>
+      </c>
+      <c r="B196" s="6">
         <v>880053</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C196" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G132" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="6">
+      <c r="H196" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>423</v>
+      </c>
+      <c r="B197" s="6">
         <v>880053</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C197" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="G133" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="6">
+      <c r="H197" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>423</v>
+      </c>
+      <c r="B198" s="6">
         <v>880053</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C198" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G134" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="6">
+      <c r="H198" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>423</v>
+      </c>
+      <c r="B199" s="6">
         <v>880055</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C199" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G135" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="6">
+      <c r="H199" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>423</v>
+      </c>
+      <c r="B200" s="6">
         <v>880055</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C200" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G136" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
+      <c r="H200" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>423</v>
+      </c>
+      <c r="B201" s="6">
         <v>880055</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C201" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G137" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="6">
+      <c r="H201" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>423</v>
+      </c>
+      <c r="B202" s="6">
         <v>880057</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C202" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G138" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="6">
+      <c r="H202" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>423</v>
+      </c>
+      <c r="B203" s="6">
         <v>880057</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C203" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="G139" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="6">
+      <c r="H203" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>423</v>
+      </c>
+      <c r="B204" s="6">
         <v>880065</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C204" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G140" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
+      <c r="H204" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>423</v>
+      </c>
+      <c r="B205" s="6">
         <v>880065</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C205" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G141" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="6">
+      <c r="H205" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>423</v>
+      </c>
+      <c r="B206" s="6">
         <v>880067</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C206" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G142" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="6">
+      <c r="H206" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>423</v>
+      </c>
+      <c r="B207" s="6">
         <v>880067</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C207" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="G143" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="H207" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>423</v>
+      </c>
+      <c r="B208" s="6">
         <v>880067</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="C208" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G144" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="6">
+      <c r="H208" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>423</v>
+      </c>
+      <c r="B209" s="6">
         <v>880067</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="C209" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G145" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="H209" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>423</v>
+      </c>
+      <c r="B210" s="6">
         <v>880071</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C210" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G146" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
+      <c r="H210" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>423</v>
+      </c>
+      <c r="B211" s="6">
         <v>880072</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C211" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G147" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="6">
+      <c r="H211" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>423</v>
+      </c>
+      <c r="B212" s="6">
         <v>880074</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C212" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G148" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="6">
+      <c r="H212" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>423</v>
+      </c>
+      <c r="B213" s="6">
         <v>880075</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="C213" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G149" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="6">
+      <c r="H213" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>423</v>
+      </c>
+      <c r="B214" s="6">
         <v>880075</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C214" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G150" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
+      <c r="H214" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>423</v>
+      </c>
+      <c r="B215" s="6">
         <v>880076</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C215" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="G151" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
+      <c r="H215" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>423</v>
+      </c>
+      <c r="B216" s="6">
         <v>880076</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C216" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G152" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
+      <c r="H216" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>423</v>
+      </c>
+      <c r="B217" s="6">
         <v>880076</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="C217" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G153" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="6">
+      <c r="H217" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>423</v>
+      </c>
+      <c r="B218" s="6">
         <v>880078</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C218" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G154" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="6">
+      <c r="H218" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>423</v>
+      </c>
+      <c r="B219" s="6">
         <v>880079</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C219" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G155" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="6">
+      <c r="H219" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>423</v>
+      </c>
+      <c r="B220" s="6">
         <v>880079</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C220" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G156" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
+      <c r="H220" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>423</v>
+      </c>
+      <c r="B221" s="6">
         <v>880079</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C221" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="D221" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G157" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="6">
+      <c r="H221" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>423</v>
+      </c>
+      <c r="B222" s="6">
         <v>880079</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C222" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="D222" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="G158" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="6">
+      <c r="H222" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>423</v>
+      </c>
+      <c r="B223" s="6">
         <v>880083</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C223" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G159" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
+      <c r="H223" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>423</v>
+      </c>
+      <c r="B224" s="6">
         <v>880086</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C224" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G160" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="6">
+      <c r="H224" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>423</v>
+      </c>
+      <c r="B225" s="6">
         <v>880086</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C225" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G161" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="6">
+      <c r="H225" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>423</v>
+      </c>
+      <c r="B226" s="6">
         <v>880086</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="C226" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G162" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="6">
+      <c r="H226" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>423</v>
+      </c>
+      <c r="B227" s="6">
         <v>880087</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C227" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G163" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
+      <c r="H227" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>423</v>
+      </c>
+      <c r="B228" s="6">
         <v>880088</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C228" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G164" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="6">
+      <c r="H228" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>423</v>
+      </c>
+      <c r="B229" s="6">
         <v>880088</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C229" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="G165" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="6">
+      <c r="H229" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>423</v>
+      </c>
+      <c r="B230" s="6">
         <v>880088</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C230" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="G166" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="6">
+      <c r="H230" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>423</v>
+      </c>
+      <c r="B231" s="6">
         <v>880089</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C231" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="G167" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="6">
+      <c r="H231" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>423</v>
+      </c>
+      <c r="B232" s="6">
         <v>880092</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C232" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G168" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
+      <c r="H232" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>423</v>
+      </c>
+      <c r="B233" s="6">
         <v>880092</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C233" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="G169" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="6">
+      <c r="H233" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>423</v>
+      </c>
+      <c r="B234" s="6">
         <v>880093</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="C234" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="G170" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="6">
+      <c r="H234" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>423</v>
+      </c>
+      <c r="B235" s="6">
         <v>880093</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C235" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G171" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="6">
+      <c r="H235" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>423</v>
+      </c>
+      <c r="B236" s="6">
         <v>880096</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C236" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="G172" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="6">
+      <c r="H236" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>423</v>
+      </c>
+      <c r="B237" s="6">
         <v>880100</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C237" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="G173" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="6">
+      <c r="H237" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>423</v>
+      </c>
+      <c r="B238" s="6">
         <v>880100</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C238" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="G174" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="6">
+      <c r="H238" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>423</v>
+      </c>
+      <c r="B239" s="6">
         <v>880100</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C239" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G175" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
+      <c r="H239" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>423</v>
+      </c>
+      <c r="B240" s="6">
         <v>880100</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C240" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G176" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
+      <c r="H240" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>423</v>
+      </c>
+      <c r="B241" s="6">
         <v>880101</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="C241" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="G177" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="6">
+      <c r="H241" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>423</v>
+      </c>
+      <c r="B242" s="6">
         <v>880102</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C242" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="D242" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G178" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="6">
+      <c r="H242" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>423</v>
+      </c>
+      <c r="B243" s="6">
         <v>880102</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C243" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="D243" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G179" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="6">
+      <c r="H243" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>423</v>
+      </c>
+      <c r="B244" s="6">
         <v>880107</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C244" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G180" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="6">
+      <c r="H244" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>423</v>
+      </c>
+      <c r="B245" s="6">
         <v>880107</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C245" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="G181" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="6">
+      <c r="H245" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>423</v>
+      </c>
+      <c r="B246" s="6">
         <v>880107</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C246" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G182" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+      <c r="H246" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>423</v>
+      </c>
+      <c r="B247" s="6">
         <v>880107</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C247" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="G183" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="6">
+      <c r="H247" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>423</v>
+      </c>
+      <c r="B248" s="6">
         <v>880108</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C248" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G184" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="6">
+      <c r="H248" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>423</v>
+      </c>
+      <c r="B249" s="6">
         <v>880108</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="C249" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G185" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="2" t="s">
+      <c r="H249" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>2016</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="C250" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="D250" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="E250" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E186" s="2" t="s">
+      <c r="F250" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F186" s="2" t="s">
+      <c r="G250" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G186" s="1" t="s">
+      <c r="H250" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>2016</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C251" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="D251" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="E251" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E187" s="1" t="s">
+      <c r="F251" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F187" s="1" t="s">
+      <c r="G251" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G187" s="1" t="s">
+      <c r="H251" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" s="2" t="s">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>2016</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C252" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="D252" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D188" s="2" t="s">
+      <c r="E252" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E188" s="1" t="s">
+      <c r="F252" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F188" s="1" t="s">
+      <c r="G252" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G188" s="1" t="s">
+      <c r="H252" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="2" t="s">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>2016</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="C253" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="D253" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D189" s="2" t="s">
+      <c r="E253" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E189" s="1" t="s">
+      <c r="F253" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F189" s="1" t="s">
+      <c r="G253" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G189" s="1" t="s">
+      <c r="H253" s="1" t="s">
         <v>227</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{C5B36CAD-FD0A-4B42-A5F0-CEDAE9F551CA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G189">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H236">
+      <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="20" type="noConversion"/>
@@ -6440,7 +8924,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF944944-0844-4FB8-99F2-9DEC0D345698}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="11" bestFit="1" customWidth="1"/>
@@ -6464,329 +8948,417 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
-        <v>330</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="C2" s="10">
-        <v>57901</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>320</v>
+      <c r="A2">
+        <v>302</v>
+      </c>
+      <c r="B2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C2">
+        <v>59002</v>
+      </c>
+      <c r="D2" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>562</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="C3" s="10">
-        <v>57068</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>322</v>
+      <c r="A3">
+        <v>315</v>
+      </c>
+      <c r="B3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C3">
+        <v>62115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
-        <v>762</v>
+        <v>330</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C4" s="10">
-        <v>7546</v>
+        <v>57901</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <v>1416</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="C5" s="10">
-        <v>56565</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>326</v>
+      <c r="A5">
+        <v>335</v>
+      </c>
+      <c r="B5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C5">
+        <v>62116</v>
+      </c>
+      <c r="D5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
-        <v>2709</v>
+        <v>562</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C6" s="10">
-        <v>58215</v>
+        <v>57068</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>2713</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C7" s="10">
-        <v>58697</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>330</v>
+      <c r="A7">
+        <v>613</v>
+      </c>
+      <c r="B7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C7">
+        <v>65978</v>
+      </c>
+      <c r="D7" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
-        <v>4076</v>
+        <v>762</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C8" s="10">
-        <v>7799</v>
+        <v>7546</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
-        <v>7254</v>
+        <v>1416</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C9" s="10">
-        <v>7294</v>
+        <v>56565</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
-        <v>7258</v>
+        <v>2709</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C10" s="10">
-        <v>7268</v>
+        <v>58215</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>7762</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="C11" s="10">
-        <v>55545</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>338</v>
+      <c r="A11">
+        <v>2709</v>
+      </c>
+      <c r="B11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C11">
+        <v>7538</v>
+      </c>
+      <c r="D11" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
-        <v>7765</v>
+        <v>2713</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C12" s="10">
-        <v>7709</v>
+        <v>58697</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>10474</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="C13" s="10">
-        <v>10397</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>342</v>
+      <c r="A13">
+        <v>3612</v>
+      </c>
+      <c r="B13" t="s">
+        <v>479</v>
+      </c>
+      <c r="C13">
+        <v>7512</v>
+      </c>
+      <c r="D13" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
-        <v>10474</v>
+        <v>4076</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C14" s="10">
-        <v>54995</v>
+        <v>7799</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>10619</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="C15" s="10">
-        <v>7784</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>345</v>
+      <c r="A15" s="11">
+        <v>7146</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C15" s="11">
+        <v>2518</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
-        <v>50030</v>
+        <v>7254</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="C16" s="10">
-        <v>1393</v>
+        <v>7294</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
-        <v>55120</v>
+        <v>7258</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="C17" s="10">
-        <v>10789</v>
+        <v>7268</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
-        <v>55306</v>
+        <v>7762</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C18" s="10">
-        <v>59338</v>
+        <v>55545</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
-        <v>55306</v>
+        <v>7765</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C19" s="10">
-        <v>59784</v>
+        <v>7709</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <v>55375</v>
+        <v>10474</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C20" s="10">
-        <v>57664</v>
+        <v>10397</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
-        <v>55481</v>
+        <v>10474</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="C21" s="10">
-        <v>58557</v>
+        <v>54995</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>55508</v>
+        <v>10619</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="C22" s="10">
-        <v>55874</v>
+        <v>7784</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
+        <v>50030</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C23" s="10">
+        <v>1393</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>55120</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="C24" s="10">
+        <v>10789</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
+        <v>55306</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="10">
+        <v>59338</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
+        <v>55306</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="10">
+        <v>59784</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>55375</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C27" s="10">
+        <v>57664</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
+        <v>55481</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C28" s="10">
+        <v>58557</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>55508</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" s="10">
+        <v>55874</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
         <v>70454</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B30" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C30" s="10">
         <v>54538</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D30" s="12" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
-        <v>7146</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C24" s="11">
-        <v>2518</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{23DBA6EA-2935-43AA-81F4-2A228D9D9EA2}"/>
+  <autoFilter ref="A1:D1" xr:uid="{23DBA6EA-2935-43AA-81F4-2A228D9D9EA2}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D30">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7783,11 +10355,59 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2021-06-22T20:59:33+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF32AD688505FB45A4B74E8374DD655E" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="820e166eda12a2b21727580e35d4b1c4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="03c14dc6-992a-47d3-9648-df74221fc344" xmlns:ns6="434a65cb-19a2-4f64-81f9-c4c3497f5b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73bb20789afc0d8257071bd90159119b" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8224,55 +10844,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2021-06-22T20:59:33+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F48335-9609-4D38-B63B-9A6620FE759C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="434a65cb-19a2-4f64-81f9-c4c3497f5b4c"/>
+    <ds:schemaRef ds:uri="03c14dc6-992a-47d3-9648-df74221fc344"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D1F9EA-526B-4162-847E-36B5EC9F2951}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B99ED44-03A6-4635-B387-C99415CE560D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
@@ -8280,7 +10881,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D1E071-1F27-41E0-9A83-EBB1CE4676B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8301,33 +10902,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F48335-9609-4D38-B63B-9A6620FE759C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="434a65cb-19a2-4f64-81f9-c4c3497f5b4c"/>
-    <ds:schemaRef ds:uri="03c14dc6-992a-47d3-9648-df74221fc344"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D1F9EA-526B-4162-847E-36B5EC9F2951}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/manual_matches.xlsx
+++ b/manual_matches.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\capd_eia_crosswalk\users\gofortht\crosswalk_repo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\eGrid\capd_eia_crosswalk\users\zhangm\camd-eia-crosswalk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94E93B8-E055-4CA7-BC07-E057045814CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8704C065-C8D8-4645-959A-26DE4D9B67D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5460" yWindow="1170" windowWidth="28800" windowHeight="7800" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_manual_matches" sheetId="1" r:id="rId1"/>
     <sheet name="unit_manual_excluded" sheetId="2" r:id="rId2"/>
     <sheet name="plant_id_manual_matches" sheetId="3" r:id="rId3"/>
-    <sheet name="further_research" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet Descriptions" sheetId="4" r:id="rId5"/>
+    <sheet name="plant_id_epa_to_eia" sheetId="6" r:id="rId4"/>
+    <sheet name="further_research" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet Descriptions" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">plant_id_manual_matches!$A$1:$D$1</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="513">
   <si>
     <t>EIA_PLANT_ID</t>
   </si>
@@ -1531,6 +1532,54 @@
   </si>
   <si>
     <t>UNIT2</t>
+  </si>
+  <si>
+    <t>epa_plant_name</t>
+  </si>
+  <si>
+    <t>epa_plant_id</t>
+  </si>
+  <si>
+    <t>epa_unit_id</t>
+  </si>
+  <si>
+    <t>eia_plant_name</t>
+  </si>
+  <si>
+    <t>eia_plant_id</t>
+  </si>
+  <si>
+    <t>eia_unit_id</t>
+  </si>
+  <si>
+    <t>AES Puerto Rico, LP</t>
+  </si>
+  <si>
+    <t>AES Puerto Rico</t>
+  </si>
+  <si>
+    <t>Aguirre Steam Power Plant</t>
+  </si>
+  <si>
+    <t>Aguirre Plant</t>
+  </si>
+  <si>
+    <t>Costa Sur Steam Power Plant</t>
+  </si>
+  <si>
+    <t>Costa Sur Plant</t>
+  </si>
+  <si>
+    <t>San Juan Steam Power Plant</t>
+  </si>
+  <si>
+    <t>Central San Juan Plant</t>
+  </si>
+  <si>
+    <t>Palo Seco Steam Power Plant</t>
+  </si>
+  <si>
+    <t>Palo Seco Plant</t>
   </si>
 </sst>
 </file>
@@ -9364,6 +9413,356 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02294E30-E5CA-4696-82B9-6506C2DB56DE}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E1" t="s">
+        <v>501</v>
+      </c>
+      <c r="F1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B2">
+        <v>880102</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E2">
+        <v>61082</v>
+      </c>
+      <c r="F2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B3">
+        <v>880102</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>504</v>
+      </c>
+      <c r="E3">
+        <v>61082</v>
+      </c>
+      <c r="F3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B4">
+        <v>880105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D4" t="s">
+        <v>506</v>
+      </c>
+      <c r="E4">
+        <v>61146</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5">
+        <v>880105</v>
+      </c>
+      <c r="C5" t="s">
+        <v>482</v>
+      </c>
+      <c r="D5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E5">
+        <v>61146</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6">
+        <v>880104</v>
+      </c>
+      <c r="C6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D6" t="s">
+        <v>508</v>
+      </c>
+      <c r="E6">
+        <v>61147</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B7">
+        <v>880104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>484</v>
+      </c>
+      <c r="D7" t="s">
+        <v>508</v>
+      </c>
+      <c r="E7">
+        <v>61147</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>507</v>
+      </c>
+      <c r="B8">
+        <v>880104</v>
+      </c>
+      <c r="C8" t="s">
+        <v>485</v>
+      </c>
+      <c r="D8" t="s">
+        <v>508</v>
+      </c>
+      <c r="E8">
+        <v>61147</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>507</v>
+      </c>
+      <c r="B9">
+        <v>880104</v>
+      </c>
+      <c r="C9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" t="s">
+        <v>508</v>
+      </c>
+      <c r="E9">
+        <v>61147</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>509</v>
+      </c>
+      <c r="B10">
+        <v>880106</v>
+      </c>
+      <c r="C10" t="s">
+        <v>487</v>
+      </c>
+      <c r="D10" t="s">
+        <v>510</v>
+      </c>
+      <c r="E10">
+        <v>61148</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>509</v>
+      </c>
+      <c r="B11">
+        <v>880106</v>
+      </c>
+      <c r="C11" t="s">
+        <v>488</v>
+      </c>
+      <c r="D11" t="s">
+        <v>510</v>
+      </c>
+      <c r="E11">
+        <v>61148</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>509</v>
+      </c>
+      <c r="B12">
+        <v>880107</v>
+      </c>
+      <c r="C12" t="s">
+        <v>489</v>
+      </c>
+      <c r="D12" t="s">
+        <v>510</v>
+      </c>
+      <c r="E12">
+        <v>61148</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>509</v>
+      </c>
+      <c r="B13">
+        <v>880108</v>
+      </c>
+      <c r="C13" t="s">
+        <v>490</v>
+      </c>
+      <c r="D13" t="s">
+        <v>510</v>
+      </c>
+      <c r="E13">
+        <v>61148</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B14">
+        <v>880103</v>
+      </c>
+      <c r="C14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D14" t="s">
+        <v>512</v>
+      </c>
+      <c r="E14">
+        <v>61149</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>511</v>
+      </c>
+      <c r="B15">
+        <v>880103</v>
+      </c>
+      <c r="C15" t="s">
+        <v>492</v>
+      </c>
+      <c r="D15" t="s">
+        <v>512</v>
+      </c>
+      <c r="E15">
+        <v>61149</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>511</v>
+      </c>
+      <c r="B16">
+        <v>880103</v>
+      </c>
+      <c r="C16" t="s">
+        <v>493</v>
+      </c>
+      <c r="D16" t="s">
+        <v>512</v>
+      </c>
+      <c r="E16">
+        <v>61149</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>511</v>
+      </c>
+      <c r="B17">
+        <v>880103</v>
+      </c>
+      <c r="C17" t="s">
+        <v>494</v>
+      </c>
+      <c r="D17" t="s">
+        <v>512</v>
+      </c>
+      <c r="E17">
+        <v>61149</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB1A3B7-CB0E-4C70-B712-DAB54E286D7C}">
   <dimension ref="A1:G112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10299,7 +10698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD10B953-F711-4F6E-8A1B-58F0D1356472}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10355,59 +10754,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2021-06-22T20:59:33+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF32AD688505FB45A4B74E8374DD655E" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="820e166eda12a2b21727580e35d4b1c4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="03c14dc6-992a-47d3-9648-df74221fc344" xmlns:ns6="434a65cb-19a2-4f64-81f9-c4c3497f5b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73bb20789afc0d8257071bd90159119b" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10844,44 +11190,60 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F48335-9609-4D38-B63B-9A6620FE759C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="434a65cb-19a2-4f64-81f9-c4c3497f5b4c"/>
-    <ds:schemaRef ds:uri="03c14dc6-992a-47d3-9648-df74221fc344"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D1F9EA-526B-4162-847E-36B5EC9F2951}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B99ED44-03A6-4635-B387-C99415CE560D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2021-06-22T20:59:33+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D1E071-1F27-41E0-9A83-EBB1CE4676B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10902,4 +11264,41 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B99ED44-03A6-4635-B387-C99415CE560D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D1F9EA-526B-4162-847E-36B5EC9F2951}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F48335-9609-4D38-B63B-9A6620FE759C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="434a65cb-19a2-4f64-81f9-c4c3497f5b4c"/>
+    <ds:schemaRef ds:uri="03c14dc6-992a-47d3-9648-df74221fc344"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>